--- a/saida/planilha/planilha_corrigida.xlsx
+++ b/saida/planilha/planilha_corrigida.xlsx
@@ -437,7 +437,7 @@
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="58" customWidth="1" min="8" max="8"/>
+    <col width="62" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -522,7 +522,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0001_(a classificar)_04-11-2022_R$5.000,00_circunstancia_cinematografica_e_prod.pdf</t>
+          <t>(a classificar)\0001_(a classificar)_04-11-2022_R$5.000,00_circunstancia_cinematografica_e_prod.pdf</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -561,7 +561,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0002_(a classificar)_04-11-2022_R$11.000,00_circunstancia_cinematografica_e_prod.pdf</t>
+          <t>(a classificar)\0002_(a classificar)_04-11-2022_R$11.000,00_circunstancia_cinematografica_e_prod.pdf</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -600,7 +600,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0003_(a classificar)_04-11-2022_R$20.000,00_circunstancia_cinematografica_e_prod.pdf</t>
+          <t>(a classificar)\0003_(a classificar)_04-11-2022_R$20.000,00_circunstancia_cinematografica_e_prod.pdf</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -639,7 +639,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0004_(a classificar)_04-11-2022_R$30.000,00_circunstancia_cinematografica_e_prod.pdf</t>
+          <t>(a classificar)\0004_(a classificar)_04-11-2022_R$30.000,00_circunstancia_cinematografica_e_prod.pdf</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -678,7 +678,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0005_(a classificar)_21-11-2022_R$800,00_luis_f_monte_cipullo.pdf</t>
+          <t>(a classificar)\0005_(a classificar)_21-11-2022_R$800,00_luis_f_monte_cipullo.pdf</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -717,7 +717,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0006_(a classificar)_28-11-2022_R$20.000,00_circunstancia_cinematografica_e_prod.pdf</t>
+          <t>(a classificar)\0006_(a classificar)_28-11-2022_R$20.000,00_circunstancia_cinematografica_e_prod.pdf</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -756,7 +756,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0007_(a classificar)_12-12-2022_R$30.000,00_circunstancia_cinematografica_e_prod.pdf</t>
+          <t>(a classificar)\0007_(a classificar)_12-12-2022_R$30.000,00_circunstancia_cinematografica_e_prod.pdf</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -795,7 +795,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0008_(a classificar)_14-12-2022_R$2.000,00_planifilmes_ltda.pdf</t>
+          <t>(a classificar)\0008_(a classificar)_14-12-2022_R$2.000,00_planifilmes_ltda.pdf</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -834,7 +834,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0009_(a classificar)_14-12-2022_R$6.000,00_julia_barbara_melo_de_sousa_40926175.pdf</t>
+          <t>(a classificar)\0009_(a classificar)_14-12-2022_R$6.000,00_julia_barbara_melo_de_sousa_40926175.pdf</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -873,7 +873,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0010_(a classificar)_20-12-2022_R$20.000,00_circunstancia_cinematografica_e_prod.pdf</t>
+          <t>(a classificar)\0010_(a classificar)_20-12-2022_R$20.000,00_circunstancia_cinematografica_e_prod.pdf</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -912,7 +912,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0011_(a classificar)_23-01-2023_R$4.500,00_circunstancia_cinematografica_e_prod.pdf</t>
+          <t>(a classificar)\0011_(a classificar)_23-01-2023_R$4.500,00_circunstancia_cinematografica_e_prod.pdf</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -951,7 +951,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0012_(a classificar)_23-01-2023_R$30.000,00_circunstancia_cinematografica_e_prod.pdf</t>
+          <t>(a classificar)\0012_(a classificar)_23-01-2023_R$30.000,00_circunstancia_cinematografica_e_prod.pdf</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -990,7 +990,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0013_(a classificar)_22-02-2023_R$19.550,00_circunstancia_cinematografica_e_prod.pdf</t>
+          <t>(a classificar)\0013_(a classificar)_22-02-2023_R$19.550,00_circunstancia_cinematografica_e_prod.pdf</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0014_(a classificar)_18-08-2023_R$380,00_radio_e_televisao_bandeirantes_s_a.pdf</t>
+          <t>(a classificar)\0014_(a classificar)_18-08-2023_R$380,00_radio_e_televisao_bandeirantes_s_a.pdf</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0015_(a classificar)_25-08-2023_R$10.500,00_memoria_coletiva_imagens_e_textos_lt.pdf</t>
+          <t>(a classificar)\0015_(a classificar)_25-08-2023_R$10.500,00_memoria_coletiva_imagens_e_textos_lt.pdf</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0016_(a classificar)_04-09-2023_R$700,00_porviroscopio_projetos_c_c_ltda.pdf</t>
+          <t>(a classificar)\0016_(a classificar)_04-09-2023_R$700,00_porviroscopio_projetos_c_c_ltda.pdf</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0017_(a classificar)_05-09-2023_R$120,00_sem_favorecido.pdf</t>
+          <t>(a classificar)\0017_(a classificar)_05-09-2023_R$120,00_sem_favorecido.pdf</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0018_(a classificar)_05-09-2023_R$33.000,00_favorecido.pdf</t>
+          <t>(a classificar)\0018_(a classificar)_05-09-2023_R$33.000,00_favorecido.pdf</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0019_(a classificar)_06-09-2023_R$4.900,00_julia_barbara_melo_de_sousa_40926175.pdf</t>
+          <t>(a classificar)\0019_(a classificar)_06-09-2023_R$4.900,00_julia_barbara_melo_de_sousa_40926175.pdf</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0020_(a classificar)_11-09-2023_R$3.000,00_ana_beatriz_hermanson_pomar_servicos.pdf</t>
+          <t>(a classificar)\0020_(a classificar)_11-09-2023_R$3.000,00_ana_beatriz_hermanson_pomar_servicos.pdf</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0021_(a classificar)_26-09-2023_R$11.250,00_filmes_de_taipa_prod.pdf</t>
+          <t>(a classificar)\0021_(a classificar)_26-09-2023_R$11.250,00_filmes_de_taipa_prod.pdf</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0022_(a classificar)_28-09-2023_R$15,30_casa_do_roadie.pdf</t>
+          <t>(a classificar)\0022_(a classificar)_28-09-2023_R$15,30_casa_do_roadie.pdf</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0023_(a classificar)_28-09-2023_R$350,00_casa_do_roadie.pdf</t>
+          <t>(a classificar)\0023_(a classificar)_28-09-2023_R$350,00_casa_do_roadie.pdf</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0024_(a classificar)_28-09-2023_R$8.800,00_cityhome_servicos_imobiliarios_ltda.pdf</t>
+          <t>(a classificar)\0024_(a classificar)_28-09-2023_R$8.800,00_cityhome_servicos_imobiliarios_ltda.pdf</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0025_(a classificar)_29-09-2023_R$35,10_scm_prest_serv_postais_ltda.pdf</t>
+          <t>(a classificar)\0025_(a classificar)_29-09-2023_R$35,10_scm_prest_serv_postais_ltda.pdf</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0026_(a classificar)_29-09-2023_R$150,00_cityhome_servicos_imobiliarios_ltda.pdf</t>
+          <t>(a classificar)\0026_(a classificar)_29-09-2023_R$150,00_cityhome_servicos_imobiliarios_ltda.pdf</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0027_(a classificar)_29-09-2023_R$500,00_cityhome_servicos_imobiliarios_ltda.pdf</t>
+          <t>(a classificar)\0027_(a classificar)_29-09-2023_R$500,00_cityhome_servicos_imobiliarios_ltda.pdf</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0028_(a classificar)_29-09-2023_R$3.116,00_matron_informatica.pdf</t>
+          <t>(a classificar)\0028_(a classificar)_29-09-2023_R$3.116,00_matron_informatica.pdf</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0029_(a classificar)_29-09-2023_R$5.768,40_pateo_moinhos_de_vento_adm_e_part_lt.pdf</t>
+          <t>(a classificar)\0029_(a classificar)_29-09-2023_R$5.768,40_pateo_moinhos_de_vento_adm_e_part_lt.pdf</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0030_(a classificar)_29-09-2023_R$35.000,00_martina_milla_raffaelli_me.pdf</t>
+          <t>(a classificar)\0030_(a classificar)_29-09-2023_R$35.000,00_martina_milla_raffaelli_me.pdf</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0031_(a classificar)_02-10-2023_R$1.610,00_pateo_moinhos_de_vento_adm_e_part_lt.pdf</t>
+          <t>(a classificar)\0031_(a classificar)_02-10-2023_R$1.610,00_pateo_moinhos_de_vento_adm_e_part_lt.pdf</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0032_(a classificar)_03-10-2023_R$200,00_glademir_m_machado.pdf</t>
+          <t>(a classificar)\0032_(a classificar)_03-10-2023_R$200,00_glademir_m_machado.pdf</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0033_(a classificar)_03-10-2023_R$3.020,00_matron_informatica.pdf</t>
+          <t>(a classificar)\0033_(a classificar)_03-10-2023_R$3.020,00_matron_informatica.pdf</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0034_(a classificar)_05-10-2023_R$500,00_amir_labaki.pdf</t>
+          <t>(a classificar)\0034_(a classificar)_05-10-2023_R$500,00_amir_labaki.pdf</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0035_(a classificar)_06-10-2023_R$10.500,00_memoria_coletiva_imagens_e_textos_lt.pdf</t>
+          <t>(a classificar)\0035_(a classificar)_06-10-2023_R$10.500,00_memoria_coletiva_imagens_e_textos_lt.pdf</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0036_(a classificar)_09-10-2023_R$1.800,00_fabio_baltar_duarte.pdf</t>
+          <t>(a classificar)\0036_(a classificar)_09-10-2023_R$1.800,00_fabio_baltar_duarte.pdf</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0037_(a classificar)_09-10-2023_R$1.800,01_fabio_baltar_duarte.pdf</t>
+          <t>(a classificar)\0037_(a classificar)_09-10-2023_R$1.800,01_fabio_baltar_duarte.pdf</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0038_(a classificar)_09-10-2023_R$4.800,00_thiago_augusto_gomas_cunha_397893948.pdf</t>
+          <t>(a classificar)\0038_(a classificar)_09-10-2023_R$4.800,00_thiago_augusto_gomas_cunha_397893948.pdf</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0039_(a classificar)_09-10-2023_R$7.500,00_luis_felipe_monte_cipullo_4425612981.pdf</t>
+          <t>(a classificar)\0039_(a classificar)_09-10-2023_R$7.500,00_luis_felipe_monte_cipullo_4425612981.pdf</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0040_(a classificar)_09-10-2023_R$9.502,77_mandala_tours.pdf</t>
+          <t>(a classificar)\0040_(a classificar)_09-10-2023_R$9.502,77_mandala_tours.pdf</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0041_(a classificar)_09-10-2023_R$13.500,00_mog_produtora.pdf</t>
+          <t>(a classificar)\0041_(a classificar)_09-10-2023_R$13.500,00_mog_produtora.pdf</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0042_(a classificar)_10-10-2023_R$2.300,00_faculdade_de_arquitetura_e_urbanismo.pdf</t>
+          <t>(a classificar)\0042_(a classificar)_10-10-2023_R$2.300,00_faculdade_de_arquitetura_e_urbanismo.pdf</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0043_(a classificar)_11-10-2023_R$400,00_aamac.pdf</t>
+          <t>(a classificar)\0043_(a classificar)_11-10-2023_R$400,00_aamac.pdf</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0044_(a classificar)_11-10-2023_R$500,00_malnes_transporte_e_producao.pdf</t>
+          <t>(a classificar)\0044_(a classificar)_11-10-2023_R$500,00_malnes_transporte_e_producao.pdf</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>0045_(a classificar)_11-10-2023_R$1.000,00_idalina_s_r_silva.pdf</t>
+          <t>(a classificar)\0045_(a classificar)_11-10-2023_R$1.000,00_idalina_s_r_silva.pdf</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0046_(a classificar)_11-10-2023_R$1.500,00_ana_beatriz_hermanson_pomar_servicos.pdf</t>
+          <t>(a classificar)\0046_(a classificar)_11-10-2023_R$1.500,00_ana_beatriz_hermanson_pomar_servicos.pdf</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>0047_(a classificar)_11-10-2023_R$4.000,00_vondoc_filmes_ltda.pdf</t>
+          <t>(a classificar)\0047_(a classificar)_11-10-2023_R$4.000,00_vondoc_filmes_ltda.pdf</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0048_(a classificar)_11-10-2023_R$9.672,00_mandala_tours.pdf</t>
+          <t>(a classificar)\0048_(a classificar)_11-10-2023_R$9.672,00_mandala_tours.pdf</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0049_(a classificar)_13-10-2023_R$300,00_ricardo_dias_santos.pdf</t>
+          <t>(a classificar)\0049_(a classificar)_13-10-2023_R$300,00_ricardo_dias_santos.pdf</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0050_(a classificar)_13-10-2023_R$1.000,00_andre_lima_manfrim.pdf</t>
+          <t>(a classificar)\0050_(a classificar)_13-10-2023_R$1.000,00_andre_lima_manfrim.pdf</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>0051_(a classificar)_13-10-2023_R$2.000,00_maga_projetos_culturais.pdf</t>
+          <t>(a classificar)\0051_(a classificar)_13-10-2023_R$2.000,00_maga_projetos_culturais.pdf</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>0052_(a classificar)_16-10-2023_R$1.100,00_luz_rio_locacao_de_equipamentos_cine.pdf</t>
+          <t>(a classificar)\0052_(a classificar)_16-10-2023_R$1.100,00_luz_rio_locacao_de_equipamentos_cine.pdf</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>0053_(a classificar)_17-10-2023_R$4.375,00_cristhiano_rodrigues_de_jesus_041338.pdf</t>
+          <t>(a classificar)\0053_(a classificar)_17-10-2023_R$4.375,00_cristhiano_rodrigues_de_jesus_041338.pdf</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>0054_(a classificar)_17-10-2023_R$4.900,00_claudia.pdf</t>
+          <t>(a classificar)\0054_(a classificar)_17-10-2023_R$4.900,00_claudia.pdf</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>0055_(a classificar)_18-10-2023_R$550,00_fernando_m_efron.pdf</t>
+          <t>(a classificar)\0055_(a classificar)_18-10-2023_R$550,00_fernando_m_efron.pdf</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>0056_(a classificar)_24-10-2023_R$9.427,38_monica_g_p_moraes.pdf</t>
+          <t>(a classificar)\0056_(a classificar)_24-10-2023_R$9.427,38_monica_g_p_moraes.pdf</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>0057_(a classificar)_25-10-2023_R$450,00_caleidoskopica_producoes.pdf</t>
+          <t>(a classificar)\0057_(a classificar)_25-10-2023_R$450,00_caleidoskopica_producoes.pdf</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>0058_(a classificar)_25-10-2023_R$600,00_sem_favorecido.pdf</t>
+          <t>(a classificar)\0058_(a classificar)_25-10-2023_R$600,00_sem_favorecido.pdf</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>0059_(a classificar)_25-10-2023_R$816,42_sofia_v_baccarini.pdf</t>
+          <t>(a classificar)\0059_(a classificar)_25-10-2023_R$816,42_sofia_v_baccarini.pdf</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>0060_(a classificar)_25-10-2023_R$1.800,00_thiago_augusto_gomas_cunha_397893948.pdf</t>
+          <t>(a classificar)\0060_(a classificar)_25-10-2023_R$1.800,00_thiago_augusto_gomas_cunha_397893948.pdf</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>0061_(a classificar)_25-10-2023_R$2.000,00_maga_projetos_culturais.pdf</t>
+          <t>(a classificar)\0061_(a classificar)_25-10-2023_R$2.000,00_maga_projetos_culturais.pdf</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>0062_(a classificar)_25-10-2023_R$3.600,00_anne_santos.pdf</t>
+          <t>(a classificar)\0062_(a classificar)_25-10-2023_R$3.600,00_anne_santos.pdf</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>0063_(a classificar)_25-10-2023_R$4.500,00_filmes_de_taipa_prod.pdf</t>
+          <t>(a classificar)\0063_(a classificar)_25-10-2023_R$4.500,00_filmes_de_taipa_prod.pdf</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>0064_(a classificar)_25-10-2023_R$4.800,00_thiago_augusto_gomas_cunha_397893948.pdf</t>
+          <t>(a classificar)\0064_(a classificar)_25-10-2023_R$4.800,00_thiago_augusto_gomas_cunha_397893948.pdf</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>0065_(a classificar)_25-10-2023_R$13.500,00_mog_produtora.pdf</t>
+          <t>(a classificar)\0065_(a classificar)_25-10-2023_R$13.500,00_mog_produtora.pdf</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>0066_(a classificar)_25-10-2023_R$20.625,00_fogo_filmes_ltda.pdf</t>
+          <t>(a classificar)\0066_(a classificar)_25-10-2023_R$20.625,00_fogo_filmes_ltda.pdf</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>0067_(a classificar)_26-10-2023_R$995,00_loc_all_de_cinema_e_televisao_limita.pdf</t>
+          <t>(a classificar)\0067_(a classificar)_26-10-2023_R$995,00_loc_all_de_cinema_e_televisao_limita.pdf</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>0068_(a classificar)_26-10-2023_R$6.550,00_grife_rio_locadora_ltda.pdf</t>
+          <t>(a classificar)\0068_(a classificar)_26-10-2023_R$6.550,00_grife_rio_locadora_ltda.pdf</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>0069_(a classificar)_26-10-2023_R$7.500,00_luis_felipe_monte_cipullo_4425612981.pdf</t>
+          <t>(a classificar)\0069_(a classificar)_26-10-2023_R$7.500,00_luis_felipe_monte_cipullo_4425612981.pdf</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>0070_(a classificar)_26-10-2023_R$11.250,00_filmes_de_taipa_prod.pdf</t>
+          <t>(a classificar)\0070_(a classificar)_26-10-2023_R$11.250,00_filmes_de_taipa_prod.pdf</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>0071_(a classificar)_30-10-2023_R$450,00_arthur_rodrigues_locacao_de_equipamento.pdf</t>
+          <t>(a classificar)\0071_(a classificar)_30-10-2023_R$450,00_arthur_rodrigues_locacao_de_equipamento.pdf</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>0072_(a classificar)_30-10-2023_R$1.500,00_martina_milla_raffaelli_me.pdf</t>
+          <t>(a classificar)\0072_(a classificar)_30-10-2023_R$1.500,00_martina_milla_raffaelli_me.pdf</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>0073_(a classificar)_30-10-2023_R$1.559,33_windsor_administracao_de_hoteis_e_se.pdf</t>
+          <t>(a classificar)\0073_(a classificar)_30-10-2023_R$1.559,33_windsor_administracao_de_hoteis_e_se.pdf</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>0074_(a classificar)_30-10-2023_R$2.529,85_windsor_administracao_de_hoteis_e_se.pdf</t>
+          <t>(a classificar)\0074_(a classificar)_30-10-2023_R$2.529,85_windsor_administracao_de_hoteis_e_se.pdf</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>0075_(a classificar)_31-10-2023_R$200,00_andre_lima_manfrim.pdf</t>
+          <t>(a classificar)\0075_(a classificar)_31-10-2023_R$200,00_andre_lima_manfrim.pdf</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>0076_(a classificar)_31-10-2023_R$320,00_jefferson_s_oliveira.pdf</t>
+          <t>(a classificar)\0076_(a classificar)_31-10-2023_R$320,00_jefferson_s_oliveira.pdf</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>0077_(a classificar)_01-11-2023_R$316,23_windsor_administracao_de_hoteis_e_se.pdf</t>
+          <t>(a classificar)\0077_(a classificar)_01-11-2023_R$316,23_windsor_administracao_de_hoteis_e_se.pdf</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>0078_(a classificar)_08-11-2023_R$4.750,00_cristhiano_rodrigues_de_jesus_041338.pdf</t>
+          <t>(a classificar)\0078_(a classificar)_08-11-2023_R$4.750,00_cristhiano_rodrigues_de_jesus_041338.pdf</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>0079_(a classificar)_14-11-2023_R$400,00_filmes_de_taipa_prod.pdf</t>
+          <t>(a classificar)\0079_(a classificar)_14-11-2023_R$400,00_filmes_de_taipa_prod.pdf</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>0080_(a classificar)_14-11-2023_R$750,00_bie_cinema_e_tv_ltda_me.pdf</t>
+          <t>(a classificar)\0080_(a classificar)_14-11-2023_R$750,00_bie_cinema_e_tv_ltda_me.pdf</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -3638,7 +3638,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>0081_(a classificar)_14-11-2023_R$27.000,00_mog_produtora.pdf</t>
+          <t>(a classificar)\0081_(a classificar)_14-11-2023_R$27.000,00_mog_produtora.pdf</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>0082_(a classificar)_27-11-2023_R$20.625,00_fogo_filmes_ltda.pdf</t>
+          <t>(a classificar)\0082_(a classificar)_27-11-2023_R$20.625,00_fogo_filmes_ltda.pdf</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>0083_(a classificar)_11-12-2023_R$2.000,00_memoria_coletiva_imagens_e_textos_lt.pdf</t>
+          <t>(a classificar)\0083_(a classificar)_11-12-2023_R$2.000,00_memoria_coletiva_imagens_e_textos_lt.pdf</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>0084_(a classificar)_20-12-2023_R$585,00_raquel_de_oliveira_lazaro_0483723061.pdf</t>
+          <t>(a classificar)\0084_(a classificar)_20-12-2023_R$585,00_raquel_de_oliveira_lazaro_0483723061.pdf</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>0085_(a classificar)_20-12-2023_R$20.625,00_fogo_filmes_ltda.pdf</t>
+          <t>(a classificar)\0085_(a classificar)_20-12-2023_R$20.625,00_fogo_filmes_ltda.pdf</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>0086_(a classificar)_24-01-2024_R$20.625,00_fogo_filmes_ltda.pdf</t>
+          <t>(a classificar)\0086_(a classificar)_24-01-2024_R$20.625,00_fogo_filmes_ltda.pdf</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>0087_(a classificar)_31-01-2024_R$487,20_in_sampa_courier_entregas_eireli.pdf</t>
+          <t>(a classificar)\0087_(a classificar)_31-01-2024_R$487,20_in_sampa_courier_entregas_eireli.pdf</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>0088_(a classificar)_23-02-2024_R$6.000,00_juba_producoes.pdf</t>
+          <t>(a classificar)\0088_(a classificar)_23-02-2024_R$6.000,00_juba_producoes.pdf</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>0089_(a classificar)_23-02-2024_R$22.500,00_fogo_filmes.pdf</t>
+          <t>(a classificar)\0089_(a classificar)_23-02-2024_R$22.500,00_fogo_filmes.pdf</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>0090_(a classificar)_07-05-2024_R$4.000,00_julia_barbara_melo_de_sousa_40926175.pdf</t>
+          <t>(a classificar)\0090_(a classificar)_07-05-2024_R$4.000,00_julia_barbara_melo_de_sousa_40926175.pdf</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>0091_(a classificar)_31-05-2024_R$5.000,00_ganzah.pdf</t>
+          <t>(a classificar)\0091_(a classificar)_31-05-2024_R$5.000,00_ganzah.pdf</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>0092_(a classificar)_03-06-2024_R$13.500,00_fogo_filmes.pdf</t>
+          <t>(a classificar)\0092_(a classificar)_03-06-2024_R$13.500,00_fogo_filmes.pdf</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>0093_(a classificar)_03-07-2024_R$5.000,00_giovana_amano.pdf</t>
+          <t>(a classificar)\0093_(a classificar)_03-07-2024_R$5.000,00_giovana_amano.pdf</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>0094_(a classificar)_30-07-2024_R$8.000,00_brasil_imagem.pdf</t>
+          <t>(a classificar)\0094_(a classificar)_30-07-2024_R$8.000,00_brasil_imagem.pdf</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>0095_(a classificar)_09-08-2024_R$550,00_biblioteca_nacional_licenciamento.pdf</t>
+          <t>(a classificar)\0095_(a classificar)_09-08-2024_R$550,00_biblioteca_nacional_licenciamento.pdf</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>0096_(a classificar)_09-08-2024_R$2.815,00_anjo_azul_filmes_ltda.pdf</t>
+          <t>(a classificar)\0096_(a classificar)_09-08-2024_R$2.815,00_anjo_azul_filmes_ltda.pdf</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>0097_(a classificar)_09-08-2024_R$2.873,00_sociedade_amigos_da_cinemateca_sac.pdf</t>
+          <t>(a classificar)\0097_(a classificar)_09-08-2024_R$2.873,00_sociedade_amigos_da_cinemateca_sac.pdf</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>0098_(a classificar)_09-08-2024_R$4.000,00_f_werneck_barcinski_ltda.pdf</t>
+          <t>(a classificar)\0098_(a classificar)_09-08-2024_R$4.000,00_f_werneck_barcinski_ltda.pdf</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -4336,7 +4336,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>0099_(a classificar)_16-08-2024_R$130,00_sem_favorecido.pdf</t>
+          <t>(a classificar)\0099_(a classificar)_16-08-2024_R$130,00_sem_favorecido.pdf</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -4375,7 +4375,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>0100_(a classificar)_19-08-2024_R$8.627,00_sociedade_amigos_da_cinemateca_sac.pdf</t>
+          <t>(a classificar)\0100_(a classificar)_19-08-2024_R$8.627,00_sociedade_amigos_da_cinemateca_sac.pdf</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>0101_(a classificar)_03-09-2024_R$600,00_camila_braune.pdf</t>
+          <t>(a classificar)\0101_(a classificar)_03-09-2024_R$600,00_camila_braune.pdf</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>0102_(a classificar)_05-09-2024_R$938,50_globo_comunicacao_e_participacoes_s_a_cnpj_27_865_757_0001_02.pdf</t>
+          <t>(a classificar)\0102_(a classificar)_05-09-2024_R$938,50_globo_comunicacao_e_participacoes_s_a_cnpj_27_865_757_0001_02.pdf</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>0103_(a classificar)_17-09-2024_R$2.250,00_lapfilme_p_c_ltda.pdf</t>
+          <t>(a classificar)\0103_(a classificar)_17-09-2024_R$2.250,00_lapfilme_p_c_ltda.pdf</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>0104_(a classificar)_17-09-2024_R$2.632,45_s_a_o_estado_de_s_paulo_cnpj_61_533_949_0001_41.pdf</t>
+          <t>(a classificar)\0104_(a classificar)_17-09-2024_R$2.632,45_s_a_o_estado_de_s_paulo_cnpj_61_533_949_0001_41.pdf</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>0105_(a classificar)_23-09-2024_R$5.500,00_sem_favorecido.pdf</t>
+          <t>(a classificar)\0105_(a classificar)_23-09-2024_R$5.500,00_sem_favorecido.pdf</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -4605,7 +4605,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>0106_(a classificar)_25-09-2024_R$6.726,23_cotacao_d_t_v_m_s_a_sefic.pdf</t>
+          <t>(a classificar)\0106_(a classificar)_25-09-2024_R$6.726,23_cotacao_d_t_v_m_s_a_sefic.pdf</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>0107_(a classificar)_30-09-2024_R$700,00_do_contribuinte.pdf</t>
+          <t>(a classificar)\0107_(a classificar)_30-09-2024_R$700,00_do_contribuinte.pdf</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>0108_(a classificar)_30-09-2024_R$2.400,00_do_contribuinte.pdf</t>
+          <t>(a classificar)\0108_(a classificar)_30-09-2024_R$2.400,00_do_contribuinte.pdf</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>0109_(a classificar)_10-10-2024_R$372,00_sociedade_amigos_da_cinemateca_sac.pdf</t>
+          <t>(a classificar)\0109_(a classificar)_10-10-2024_R$372,00_sociedade_amigos_da_cinemateca_sac.pdf</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>0110_(a classificar)_10-10-2024_R$1.836,22_cotacao_d_t_v_m_s_a_sefic.pdf</t>
+          <t>(a classificar)\0110_(a classificar)_10-10-2024_R$1.836,22_cotacao_d_t_v_m_s_a_sefic.pdf</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>0111_(a classificar)_31-10-2024_R$5.000,00_porviroscopio_projetos_c_c_ltda.pdf</t>
+          <t>(a classificar)\0111_(a classificar)_31-10-2024_R$5.000,00_porviroscopio_projetos_c_c_ltda.pdf</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>0112_(a classificar)_31-10-2024_R$5.500,00_caliban_producoes_cinematograficas_l.pdf</t>
+          <t>(a classificar)\0112_(a classificar)_31-10-2024_R$5.500,00_caliban_producoes_cinematograficas_l.pdf</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -4874,7 +4874,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>0113_(a classificar)_01-11-2024_R$140,00_do_contribuinte.pdf</t>
+          <t>(a classificar)\0113_(a classificar)_01-11-2024_R$140,00_do_contribuinte.pdf</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>0114_(a classificar)_04-11-2024_R$400,00_do_contribuinte.pdf</t>
+          <t>(a classificar)\0114_(a classificar)_04-11-2024_R$400,00_do_contribuinte.pdf</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>0115_(a classificar)_08-11-2024_R$600,00_echo_s_comunicacao_sonora_e_visual.pdf</t>
+          <t>(a classificar)\0115_(a classificar)_08-11-2024_R$600,00_echo_s_comunicacao_sonora_e_visual.pdf</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>0116_(a classificar)_08-11-2024_R$1.000,00_roberto_f_d_avila.pdf</t>
+          <t>(a classificar)\0116_(a classificar)_08-11-2024_R$1.000,00_roberto_f_d_avila.pdf</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>0117_(a classificar)_12-11-2024_R$12,00_do_contribuinte.pdf</t>
+          <t>(a classificar)\0117_(a classificar)_12-11-2024_R$12,00_do_contribuinte.pdf</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -5065,7 +5065,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>0118_(a classificar)_14-11-2024_R$200,00_do_contribuinte.pdf</t>
+          <t>(a classificar)\0118_(a classificar)_14-11-2024_R$200,00_do_contribuinte.pdf</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>0119_(a classificar)_28-11-2024_R$230,00_marach_servicos_audiovisuais_eireli.pdf</t>
+          <t>(a classificar)\0119_(a classificar)_28-11-2024_R$230,00_marach_servicos_audiovisuais_eireli.pdf</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>0120_(a classificar)_05-12-2024_R$1.500,00_geisa_silva_jesus.pdf</t>
+          <t>(a classificar)\0120_(a classificar)_05-12-2024_R$1.500,00_geisa_silva_jesus.pdf</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -5182,7 +5182,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>0121_(a classificar)_05-12-2024_R$6.400,00_sem_favorecido.pdf</t>
+          <t>(a classificar)\0121_(a classificar)_05-12-2024_R$6.400,00_sem_favorecido.pdf</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>0122_(a classificar)_10-12-2024_R$100,00_sem_favorecido.pdf</t>
+          <t>(a classificar)\0122_(a classificar)_10-12-2024_R$100,00_sem_favorecido.pdf</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>0123_(a classificar)_17-12-2024_R$2.000,00_som_livre.pdf</t>
+          <t>(a classificar)\0123_(a classificar)_17-12-2024_R$2.000,00_som_livre.pdf</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>0124_(a classificar)_17-12-2024_R$3.000,00_editora_e_importadora_musical_fermat.pdf</t>
+          <t>(a classificar)\0124_(a classificar)_17-12-2024_R$3.000,00_editora_e_importadora_musical_fermat.pdf</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>0125_(a classificar)_17-12-2024_R$3.500,00_carlos_lyra_edicoes_musicais.pdf</t>
+          <t>(a classificar)\0125_(a classificar)_17-12-2024_R$3.500,00_carlos_lyra_edicoes_musicais.pdf</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>0126_(a classificar)_17-12-2024_R$8.393,30_cotacao_d_t_v_m_s_a_sefic.pdf</t>
+          <t>(a classificar)\0126_(a classificar)_17-12-2024_R$8.393,30_cotacao_d_t_v_m_s_a_sefic.pdf</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>0127_(a classificar)_26-12-2024_R$5.000,00_giovana_amano.pdf</t>
+          <t>(a classificar)\0127_(a classificar)_26-12-2024_R$5.000,00_giovana_amano.pdf</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>0128_(a classificar)_16-01-2025_R$50,00_arquivo_nacional_licenciamento.pdf</t>
+          <t>(a classificar)\0128_(a classificar)_16-01-2025_R$50,00_arquivo_nacional_licenciamento.pdf</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>0129_(a classificar)_27-02-2025_R$7.000,00_ganzah.pdf</t>
+          <t>(a classificar)\0129_(a classificar)_27-02-2025_R$7.000,00_ganzah.pdf</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -5533,7 +5533,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>0130_(a classificar)_25-03-2025_R$626,30_sem_favorecido.pdf</t>
+          <t>(a classificar)\0130_(a classificar)_25-03-2025_R$626,30_sem_favorecido.pdf</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>0131_(a classificar)_30-04-2025_R$1.200,00_planifilmes_ltda.pdf</t>
+          <t>(a classificar)\0131_(a classificar)_30-04-2025_R$1.200,00_planifilmes_ltda.pdf</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>0132_(a classificar)_30-04-2025_R$3.000,00_giovana_amano.pdf</t>
+          <t>(a classificar)\0132_(a classificar)_30-04-2025_R$3.000,00_giovana_amano.pdf</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -5650,7 +5650,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>0133_(a classificar)_07-05-2025_R$18.093,63_fogo_filmes.pdf</t>
+          <t>(a classificar)\0133_(a classificar)_07-05-2025_R$18.093,63_fogo_filmes.pdf</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>0134_(a classificar)_10-11-2022_R$1.200,00_felipe_g_rosa.pdf</t>
+          <t>(a classificar)\0134_(a classificar)_10-11-2022_R$1.200,00_felipe_g_rosa.pdf</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>0135_(a classificar)_10-11-2022_R$1.200,00_luis_felipe_labaki.pdf</t>
+          <t>(a classificar)\0135_(a classificar)_10-11-2022_R$1.200,00_luis_felipe_labaki.pdf</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -5767,7 +5767,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>0136_(a classificar)_03-07-2023_R$25.000,00_mog_produtora.pdf</t>
+          <t>(a classificar)\0136_(a classificar)_03-07-2023_R$25.000,00_mog_produtora.pdf</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>0137_(a classificar)_03-07-2023_R$25.000,00_circunstancia_cinematografica_e_prod.pdf</t>
+          <t>(a classificar)\0137_(a classificar)_03-07-2023_R$25.000,00_circunstancia_cinematografica_e_prod.pdf</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -5845,7 +5845,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>0138_(a classificar)_28-09-2023_R$1.000,00_sofia_v_baccarini.pdf</t>
+          <t>(a classificar)\0138_(a classificar)_28-09-2023_R$1.000,00_sofia_v_baccarini.pdf</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>0139_(a classificar)_28-09-2023_R$1.000,00_andre_lima_manfrim.pdf</t>
+          <t>(a classificar)\0139_(a classificar)_28-09-2023_R$1.000,00_andre_lima_manfrim.pdf</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -5923,7 +5923,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>0140_(a classificar)_29-09-2023_R$560,00_sofia_v_baccarini.pdf</t>
+          <t>(a classificar)\0140_(a classificar)_29-09-2023_R$560,00_sofia_v_baccarini.pdf</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -5962,7 +5962,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>0141_(a classificar)_29-09-2023_R$560,00_fabio_baltar_duarte.pdf</t>
+          <t>(a classificar)\0141_(a classificar)_29-09-2023_R$560,00_fabio_baltar_duarte.pdf</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>0142_(a classificar)_29-09-2023_R$1.050,00_luis_f_monte_cipullo.pdf</t>
+          <t>(a classificar)\0142_(a classificar)_29-09-2023_R$1.050,00_luis_f_monte_cipullo.pdf</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>0143_(a classificar)_29-09-2023_R$1.050,00_felipe_g_rosa.pdf</t>
+          <t>(a classificar)\0143_(a classificar)_29-09-2023_R$1.050,00_felipe_g_rosa.pdf</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>0144_(a classificar)_29-09-2023_R$1.050,00_thiago_a_gomas_cunha.pdf</t>
+          <t>(a classificar)\0144_(a classificar)_29-09-2023_R$1.050,00_thiago_a_gomas_cunha.pdf</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>0145_(a classificar)_29-09-2023_R$1.050,00_andre_lima_monfrini.pdf</t>
+          <t>(a classificar)\0145_(a classificar)_29-09-2023_R$1.050,00_andre_lima_monfrini.pdf</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -6157,7 +6157,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>0146_(a classificar)_05-10-2023_R$700,00_edson_de_camargo_transportes.pdf</t>
+          <t>(a classificar)\0146_(a classificar)_05-10-2023_R$700,00_edson_de_camargo_transportes.pdf</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -6196,7 +6196,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>0147_(a classificar)_09-10-2023_R$240,00_luis_f_monte_cipullo.pdf</t>
+          <t>(a classificar)\0147_(a classificar)_09-10-2023_R$240,00_luis_f_monte_cipullo.pdf</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>0148_(a classificar)_09-10-2023_R$240,00_andre_lima_monfrini.pdf</t>
+          <t>(a classificar)\0148_(a classificar)_09-10-2023_R$240,00_andre_lima_monfrini.pdf</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>0149_(a classificar)_09-10-2023_R$240,00_felipe_g_rosa.pdf</t>
+          <t>(a classificar)\0149_(a classificar)_09-10-2023_R$240,00_felipe_g_rosa.pdf</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -6313,7 +6313,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>0150_(a classificar)_09-10-2023_R$240,00_thiago_a_gomas_cunha.pdf</t>
+          <t>(a classificar)\0150_(a classificar)_09-10-2023_R$240,00_thiago_a_gomas_cunha.pdf</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>0151_(a classificar)_13-10-2023_R$480,00_idalina_s_r_silva.pdf</t>
+          <t>(a classificar)\0151_(a classificar)_13-10-2023_R$480,00_idalina_s_r_silva.pdf</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>0152_(a classificar)_13-10-2023_R$480,00_anne_c_melo_santos.pdf</t>
+          <t>(a classificar)\0152_(a classificar)_13-10-2023_R$480,00_anne_c_melo_santos.pdf</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>0153_(a classificar)_13-10-2023_R$1.200,00_andre_lima_monfrini.pdf</t>
+          <t>(a classificar)\0153_(a classificar)_13-10-2023_R$1.200,00_andre_lima_monfrini.pdf</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>0154_(a classificar)_13-10-2023_R$1.200,00_felipe_g_rosa.pdf</t>
+          <t>(a classificar)\0154_(a classificar)_13-10-2023_R$1.200,00_felipe_g_rosa.pdf</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>0155_(a classificar)_13-10-2023_R$1.200,00_luis_f_monte_cipullo.pdf</t>
+          <t>(a classificar)\0155_(a classificar)_13-10-2023_R$1.200,00_luis_f_monte_cipullo.pdf</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -6547,7 +6547,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>0156_(a classificar)_13-10-2023_R$1.200,00_thiago_a_gomas_cunha.pdf</t>
+          <t>(a classificar)\0156_(a classificar)_13-10-2023_R$1.200,00_thiago_a_gomas_cunha.pdf</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>0157_(a classificar)_31-10-2023_R$1.020,00_felipe_g_rosa.pdf</t>
+          <t>(a classificar)\0157_(a classificar)_31-10-2023_R$1.020,00_felipe_g_rosa.pdf</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -6625,7 +6625,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>0158_(a classificar)_31-10-2023_R$1.020,00_luis_f_monte_cipullo.pdf</t>
+          <t>(a classificar)\0158_(a classificar)_31-10-2023_R$1.020,00_luis_f_monte_cipullo.pdf</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -6664,7 +6664,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>0159_(a classificar)_31-10-2023_R$1.020,00_andre_lima_monfrini.pdf</t>
+          <t>(a classificar)\0159_(a classificar)_31-10-2023_R$1.020,00_andre_lima_monfrini.pdf</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -6703,7 +6703,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>0160_(a classificar)_08-11-2023_R$300,00_bernardo_t_s_costa.pdf</t>
+          <t>(a classificar)\0160_(a classificar)_08-11-2023_R$300,00_bernardo_t_s_costa.pdf</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -6736,11 +6736,7 @@
           <t>AMBIGUO</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>0161_(a classificar)_20-09-2023_R$1.524,64_gol_linhas_aereas.pdf</t>
-        </is>
-      </c>
+      <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr">
         <is>
           <t>débito disputado por comprovantes: GOL LINHAS AEREAS</t>
@@ -6775,11 +6771,7 @@
           <t>AMBIGUO</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>0162_(a classificar)_20-09-2023_R$1.524,64_gol_linhas_aereas.pdf</t>
-        </is>
-      </c>
+      <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
           <t>débito disputado por comprovantes: GOL LINHAS AEREAS</t>
@@ -6814,11 +6806,7 @@
           <t>AMBIGUO</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>0163_(a classificar)_20-09-2023_R$1.524,64_gol_linhas_aereas.pdf</t>
-        </is>
-      </c>
+      <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr">
         <is>
           <t>débito disputado por comprovantes: GOL LINHAS AEREAS</t>
@@ -6853,11 +6841,7 @@
           <t>AMBIGUO</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>0164_(a classificar)_20-09-2023_R$1.524,64_gol_linhas_aereas.pdf</t>
-        </is>
-      </c>
+      <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr">
         <is>
           <t>débito disputado por comprovantes: GOL LINHAS AEREAS</t>
@@ -6892,11 +6876,7 @@
           <t>AMBIGUO</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>0165_(a classificar)_20-09-2023_R$2.870,87_gol_linhas_aereas.pdf</t>
-        </is>
-      </c>
+      <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr">
         <is>
           <t>débito disputado por comprovantes: GOL LINHAS AEREAS</t>
@@ -6931,11 +6911,7 @@
           <t>AMBIGUO</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>0166_(a classificar)_20-09-2023_R$2.870,87_gol_linhas_aereas.pdf</t>
-        </is>
-      </c>
+      <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr">
         <is>
           <t>débito disputado por comprovantes: GOL LINHAS AEREAS</t>
@@ -6970,11 +6946,7 @@
           <t>AMBIGUO</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>0167_(a classificar)_20-09-2023_R$2.870,87_gol_linhas_aereas.pdf</t>
-        </is>
-      </c>
+      <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr">
         <is>
           <t>débito disputado por comprovantes: GOL LINHAS AEREAS</t>
@@ -7009,11 +6981,7 @@
           <t>AMBIGUO</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>0168_(a classificar)_20-09-2023_R$2.870,87_gol_linhas_aereas.pdf</t>
-        </is>
-      </c>
+      <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr">
         <is>
           <t>débito disputado por comprovantes: GOL LINHAS AEREAS</t>
@@ -7048,11 +7016,7 @@
           <t>AMBIGUO</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>0169_(a classificar)_09-10-2023_R$945,49_amir_labaki.pdf</t>
-        </is>
-      </c>
+      <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr">
         <is>
           <t>débito disputado por comprovantes: AMIR LABAKI</t>
@@ -7087,11 +7051,7 @@
           <t>AMBIGUO</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>0170_(a classificar)_16-10-2023_R$3.000,00_camila_licariao_de_carvalh.pdf</t>
-        </is>
-      </c>
+      <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr">
         <is>
           <t>débito disputado por comprovantes: CAMILA LICARIAO DE CARVALHO BRAUNE 4</t>
@@ -7126,11 +7086,7 @@
           <t>AMBIGUO</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>0171_(a classificar)_25-10-2023_R$10.000,00_mog_produtora.pdf</t>
-        </is>
-      </c>
+      <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr">
         <is>
           <t>débito disputado por comprovantes: MOG PRODUTORA</t>
@@ -7165,11 +7121,7 @@
           <t>AMBIGUO</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>0172_(a classificar)_14-11-2023_R$3.724,74_monica_guimaraes_p_moraes.pdf</t>
-        </is>
-      </c>
+      <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr">
         <is>
           <t>débito disputado por comprovantes: MONICA G P MORAES</t>
@@ -7204,11 +7156,7 @@
           <t>AMBIGUO</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>0173_(a classificar)_03-02-2025_R$975,04_banco_rendimento_s_a.pdf</t>
-        </is>
-      </c>
+      <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr">
         <is>
           <t>débito disputado por comprovantes: BANCO RENDIMENTO S A</t>
@@ -7243,11 +7191,7 @@
           <t>AMBIGUO</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>0174_(a classificar)_03-02-2025_R$975,04_banco_rendimento_s_a.pdf</t>
-        </is>
-      </c>
+      <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr">
         <is>
           <t>débito disputado por comprovantes: BANCO RENDIMENTO S A</t>
@@ -7288,7 +7232,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>0175_(a classificar)_20-09-2023_R$1.524,64_gol_linhas_aereas.pdf</t>
+          <t>(a classificar)\0175_(a classificar)_20-09-2023_R$1.524,64_gol_linhas_aereas.pdf</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -7331,7 +7275,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>0176_(a classificar)_20-09-2023_R$1.524,64_gol_linhas_aereas.pdf</t>
+          <t>(a classificar)\0176_(a classificar)_20-09-2023_R$1.524,64_gol_linhas_aereas.pdf</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -7374,7 +7318,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>0177_(a classificar)_20-09-2023_R$1.524,64_gol_linhas_aereas.pdf</t>
+          <t>(a classificar)\0177_(a classificar)_20-09-2023_R$1.524,64_gol_linhas_aereas.pdf</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -7417,7 +7361,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>0178_(a classificar)_20-09-2023_R$1.524,64_gol_linhas_aereas.pdf</t>
+          <t>(a classificar)\0178_(a classificar)_20-09-2023_R$1.524,64_gol_linhas_aereas.pdf</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -7460,7 +7404,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>0179_(a classificar)_20-09-2023_R$2.870,87_gol_linhas_aereas.pdf</t>
+          <t>(a classificar)\0179_(a classificar)_20-09-2023_R$2.870,87_gol_linhas_aereas.pdf</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -7503,7 +7447,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>0180_(a classificar)_20-09-2023_R$2.870,87_gol_linhas_aereas.pdf</t>
+          <t>(a classificar)\0180_(a classificar)_20-09-2023_R$2.870,87_gol_linhas_aereas.pdf</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -7546,7 +7490,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>0181_(a classificar)_20-09-2023_R$2.870,87_gol_linhas_aereas.pdf</t>
+          <t>(a classificar)\0181_(a classificar)_20-09-2023_R$2.870,87_gol_linhas_aereas.pdf</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -7589,7 +7533,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>0182_(a classificar)_20-09-2023_R$2.870,87_gol_linhas_aereas.pdf</t>
+          <t>(a classificar)\0182_(a classificar)_20-09-2023_R$2.870,87_gol_linhas_aereas.pdf</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -7632,7 +7576,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>0183_(a classificar)_09-10-2023_R$945,49_amir_labaki.pdf</t>
+          <t>(a classificar)\0183_(a classificar)_09-10-2023_R$945,49_amir_labaki.pdf</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -7675,7 +7619,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>0184_(a classificar)_09-10-2023_R$945,49_amir_labaki.pdf</t>
+          <t>(a classificar)\0184_(a classificar)_09-10-2023_R$945,49_amir_labaki.pdf</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -7718,7 +7662,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>0185_(a classificar)_16-10-2023_R$3.000,00_camila_licariao_de_carvalho_braune_4.pdf</t>
+          <t>(a classificar)\0185_(a classificar)_16-10-2023_R$3.000,00_camila_licariao_de_carvalho_braune_4.pdf</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -7761,7 +7705,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>0186_(a classificar)_16-10-2023_R$3.000,00_camila_licariao_de_carvalho_braune_4.pdf</t>
+          <t>(a classificar)\0186_(a classificar)_16-10-2023_R$3.000,00_camila_licariao_de_carvalho_braune_4.pdf</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -7804,7 +7748,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>0187_(a classificar)_25-10-2023_R$10.000,00_mog_produtora.pdf</t>
+          <t>(a classificar)\0187_(a classificar)_25-10-2023_R$10.000,00_mog_produtora.pdf</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -7847,7 +7791,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>0188_(a classificar)_25-10-2023_R$10.000,00_mog_produtora.pdf</t>
+          <t>(a classificar)\0188_(a classificar)_25-10-2023_R$10.000,00_mog_produtora.pdf</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -7890,7 +7834,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>0189_(a classificar)_14-11-2023_R$3.724,74_monica_g_p_moraes.pdf</t>
+          <t>(a classificar)\0189_(a classificar)_14-11-2023_R$3.724,74_monica_g_p_moraes.pdf</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -7933,7 +7877,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>0190_(a classificar)_14-11-2023_R$3.724,74_monica_g_p_moraes.pdf</t>
+          <t>(a classificar)\0190_(a classificar)_14-11-2023_R$3.724,74_monica_g_p_moraes.pdf</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -7976,7 +7920,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>0191_(a classificar)_03-02-2025_R$975,04_banco_rendimento_s_a.pdf</t>
+          <t>(a classificar)\0191_(a classificar)_03-02-2025_R$975,04_banco_rendimento_s_a.pdf</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -8019,7 +7963,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>0192_(a classificar)_30-10-2023_R$211,50_brilho.pdf</t>
+          <t>PENDENTES\111 - 30-10-2023 - Brilho - Equipamento Luz (diária extra).pdf</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -8056,11 +8000,7 @@
           <t>SEM-COMPROVANTE</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>0193_(a classificar)_05-10-2023_R$700,00_edson_de_camargo.pdf</t>
-        </is>
-      </c>
+      <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
           <t>comprovante do mesmo valor na data já vinculado a outro débito</t>
@@ -8095,11 +8035,7 @@
           <t>SEM-COMPROVANTE</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>0194_(a classificar)_10-10-2023_R$500,00_andre_lima_monfrini.pdf</t>
-        </is>
-      </c>
+      <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
           <t>data/valor não bate</t>
@@ -8134,11 +8070,7 @@
           <t>SEM-COMPROVANTE</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>0195_(a classificar)_08-11-2023_R$300,00_bernardo_tavares_rosa.pdf</t>
-        </is>
-      </c>
+      <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
           <t>comprovante do mesmo valor na data já vinculado a outro débito</t>
@@ -8173,11 +8105,7 @@
           <t>SEM-COMPROVANTE</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>0196_(a classificar)_26-09-2023_R$10.000,00_luis_felipe_labaki.pdf</t>
-        </is>
-      </c>
+      <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
           <t>data/valor não bate</t>
@@ -8212,11 +8140,7 @@
           <t>SEM-COMPROVANTE</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>0197_(a classificar)_26-09-2023_R$3.000,00_ana_beatriz_hermanson_poma.pdf</t>
-        </is>
-      </c>
+      <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
           <t>data/valor não bate</t>
@@ -8251,11 +8175,7 @@
           <t>SEM-COMPROVANTE</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>0198_(a classificar)_03-02-2025_R$975,04_circunstanc_1961_fsampjfn.pdf</t>
-        </is>
-      </c>
+      <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
           <t>comprovante do mesmo valor na data já vinculado a outro débito</t>

--- a/saida/planilha/planilha_corrigida.xlsx
+++ b/saida/planilha/planilha_corrigida.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Pagamentos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pagamentos'!$A$1:$I$199</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pagamentos'!$A$1:$I$186</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I199"/>
+  <dimension ref="A1:I186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Felipe G Rosa</t>
+          <t>Luis Felipe Labaki</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(a classificar)\0134_(a classificar)_10-11-2022_R$1.200,00_felipe_g_rosa.pdf</t>
+          <t>(a classificar)\0134_(a classificar)_10-11-2022_R$1.200,00_luis_felipe_labaki.pdf</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Luis Felipe Labaki</t>
+          <t>Felipe G Rosa</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(a classificar)\0135_(a classificar)_10-11-2022_R$1.200,00_luis_felipe_labaki.pdf</t>
+          <t>(a classificar)\0135_(a classificar)_10-11-2022_R$1.200,00_felipe_g_rosa.pdf</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -5744,7 +5744,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Mog Produtora</t>
+          <t>Circunstancia Cinematografica e Prod</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(a classificar)\0136_(a classificar)_03-07-2023_R$25.000,00_mog_produtora.pdf</t>
+          <t>(a classificar)\0136_(a classificar)_03-07-2023_R$25.000,00_circunstancia_cinematografica_e_prod.pdf</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -5783,7 +5783,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Circunstancia Cinematografica e Prod</t>
+          <t>Mog Produtora</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(a classificar)\0137_(a classificar)_03-07-2023_R$25.000,00_circunstancia_cinematografica_e_prod.pdf</t>
+          <t>(a classificar)\0137_(a classificar)_03-07-2023_R$25.000,00_mog_produtora.pdf</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -5817,12 +5817,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Sofia V Baccarini</t>
+          <t>Gol Linhas Aéreas</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -5836,7 +5836,7 @@
         </is>
       </c>
       <c r="F139" s="2" t="n">
-        <v>1000</v>
+        <v>1524.64</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(a classificar)\0138_(a classificar)_28-09-2023_R$1.000,00_sofia_v_baccarini.pdf</t>
+          <t>(a classificar)\0138_(a classificar)_20-09-2023_R$1.524,64_gol_linhas_aereas.pdf</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Andre Lima Manfrim</t>
+          <t>Gol Linhas Aéreas</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="F140" s="2" t="n">
-        <v>1000</v>
+        <v>1524.64</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(a classificar)\0139_(a classificar)_28-09-2023_R$1.000,00_andre_lima_manfrim.pdf</t>
+          <t>(a classificar)\0139_(a classificar)_20-09-2023_R$1.524,64_gol_linhas_aereas.pdf</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -5895,12 +5895,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2023-09-29</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Sofia V Baccarini</t>
+          <t>Gol Linhas Aéreas</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -5914,7 +5914,7 @@
         </is>
       </c>
       <c r="F141" s="2" t="n">
-        <v>560</v>
+        <v>1524.64</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(a classificar)\0140_(a classificar)_29-09-2023_R$560,00_sofia_v_baccarini.pdf</t>
+          <t>(a classificar)\0140_(a classificar)_20-09-2023_R$1.524,64_gol_linhas_aereas.pdf</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -5934,12 +5934,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2023-09-29</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Fabio Baltar Duarte</t>
+          <t>Gol Linhas Aéreas</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="F142" s="2" t="n">
-        <v>560</v>
+        <v>1524.64</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(a classificar)\0141_(a classificar)_29-09-2023_R$560,00_fabio_baltar_duarte.pdf</t>
+          <t>(a classificar)\0141_(a classificar)_20-09-2023_R$1.524,64_gol_linhas_aereas.pdf</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2023-09-29</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Luis F Monte Cipullo</t>
+          <t>Gol Linhas Aéreas</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -5992,7 +5992,7 @@
         </is>
       </c>
       <c r="F143" s="2" t="n">
-        <v>1050</v>
+        <v>2870.87</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(a classificar)\0142_(a classificar)_29-09-2023_R$1.050,00_luis_f_monte_cipullo.pdf</t>
+          <t>(a classificar)\0142_(a classificar)_20-09-2023_R$2.870,87_gol_linhas_aereas.pdf</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -6012,12 +6012,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2023-09-29</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Felipe G Rosa</t>
+          <t>Gol Linhas Aéreas</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -6031,7 +6031,7 @@
         </is>
       </c>
       <c r="F144" s="2" t="n">
-        <v>1050</v>
+        <v>2870.87</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(a classificar)\0143_(a classificar)_29-09-2023_R$1.050,00_felipe_g_rosa.pdf</t>
+          <t>(a classificar)\0143_(a classificar)_20-09-2023_R$2.870,87_gol_linhas_aereas.pdf</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -6051,12 +6051,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2023-09-29</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Thiago A Gomas Cunha</t>
+          <t>Gol Linhas Aéreas</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -6070,7 +6070,7 @@
         </is>
       </c>
       <c r="F145" s="2" t="n">
-        <v>1050</v>
+        <v>2870.87</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(a classificar)\0144_(a classificar)_29-09-2023_R$1.050,00_thiago_a_gomas_cunha.pdf</t>
+          <t>(a classificar)\0144_(a classificar)_20-09-2023_R$2.870,87_gol_linhas_aereas.pdf</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -6090,12 +6090,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2023-09-29</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Andre Lima Monfrini</t>
+          <t>Gol Linhas Aéreas</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -6109,7 +6109,7 @@
         </is>
       </c>
       <c r="F146" s="2" t="n">
-        <v>1050</v>
+        <v>2870.87</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(a classificar)\0145_(a classificar)_29-09-2023_R$1.050,00_andre_lima_monfrini.pdf</t>
+          <t>(a classificar)\0145_(a classificar)_20-09-2023_R$2.870,87_gol_linhas_aereas.pdf</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -6129,12 +6129,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Edson de Camargo Transportes</t>
+          <t>Andre Lima Manfrim</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -6148,7 +6148,7 @@
         </is>
       </c>
       <c r="F147" s="2" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(a classificar)\0146_(a classificar)_05-10-2023_R$700,00_edson_de_camargo_transportes.pdf</t>
+          <t>(a classificar)\0146_(a classificar)_28-09-2023_R$1.000,00_andre_lima_manfrim.pdf</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -6168,12 +6168,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2023-10-09</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Luis F Monte Cipullo</t>
+          <t>Sofia V Baccarini</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -6187,7 +6187,7 @@
         </is>
       </c>
       <c r="F148" s="2" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(a classificar)\0147_(a classificar)_09-10-2023_R$240,00_luis_f_monte_cipullo.pdf</t>
+          <t>(a classificar)\0147_(a classificar)_28-09-2023_R$1.000,00_sofia_v_baccarini.pdf</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -6207,12 +6207,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2023-10-09</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Andre Lima Monfrini</t>
+          <t>Fabio Baltar Duarte</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="F149" s="2" t="n">
-        <v>240</v>
+        <v>560</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(a classificar)\0148_(a classificar)_09-10-2023_R$240,00_andre_lima_monfrini.pdf</t>
+          <t>(a classificar)\0148_(a classificar)_29-09-2023_R$560,00_fabio_baltar_duarte.pdf</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -6246,12 +6246,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2023-10-09</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Felipe G Rosa</t>
+          <t>Sofia V Baccarini</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c r="F150" s="2" t="n">
-        <v>240</v>
+        <v>560</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(a classificar)\0149_(a classificar)_09-10-2023_R$240,00_felipe_g_rosa.pdf</t>
+          <t>(a classificar)\0149_(a classificar)_29-09-2023_R$560,00_sofia_v_baccarini.pdf</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -6285,12 +6285,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2023-10-09</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Thiago A Gomas Cunha</t>
+          <t>Luis F Monte Cipullo</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -6304,7 +6304,7 @@
         </is>
       </c>
       <c r="F151" s="2" t="n">
-        <v>240</v>
+        <v>1050</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(a classificar)\0150_(a classificar)_09-10-2023_R$240,00_thiago_a_gomas_cunha.pdf</t>
+          <t>(a classificar)\0150_(a classificar)_29-09-2023_R$1.050,00_luis_f_monte_cipullo.pdf</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Idalina S R Silva</t>
+          <t>Thiago A Gomas Cunha</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -6343,7 +6343,7 @@
         </is>
       </c>
       <c r="F152" s="2" t="n">
-        <v>480</v>
+        <v>1050</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(a classificar)\0151_(a classificar)_13-10-2023_R$480,00_idalina_s_r_silva.pdf</t>
+          <t>(a classificar)\0151_(a classificar)_29-09-2023_R$1.050,00_thiago_a_gomas_cunha.pdf</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -6363,12 +6363,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Anne C Melo Santos</t>
+          <t>Andre Lima Monfrini</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -6382,7 +6382,7 @@
         </is>
       </c>
       <c r="F153" s="2" t="n">
-        <v>480</v>
+        <v>1050</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(a classificar)\0152_(a classificar)_13-10-2023_R$480,00_anne_c_melo_santos.pdf</t>
+          <t>(a classificar)\0152_(a classificar)_29-09-2023_R$1.050,00_andre_lima_monfrini.pdf</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -6402,12 +6402,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Andre Lima Monfrini</t>
+          <t>Felipe G Rosa</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -6421,7 +6421,7 @@
         </is>
       </c>
       <c r="F154" s="2" t="n">
-        <v>1200</v>
+        <v>1050</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(a classificar)\0153_(a classificar)_13-10-2023_R$1.200,00_andre_lima_monfrini.pdf</t>
+          <t>(a classificar)\0153_(a classificar)_29-09-2023_R$1.050,00_felipe_g_rosa.pdf</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Felipe G Rosa</t>
+          <t>Edson de Camargo Transportes</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -6460,7 +6460,7 @@
         </is>
       </c>
       <c r="F155" s="2" t="n">
-        <v>1200</v>
+        <v>700</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(a classificar)\0154_(a classificar)_13-10-2023_R$1.200,00_felipe_g_rosa.pdf</t>
+          <t>(a classificar)\0154_(a classificar)_05-10-2023_R$700,00_edson_de_camargo_transportes.pdf</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2023-10-09</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -6499,7 +6499,7 @@
         </is>
       </c>
       <c r="F156" s="2" t="n">
-        <v>1200</v>
+        <v>240</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(a classificar)\0155_(a classificar)_13-10-2023_R$1.200,00_luis_f_monte_cipullo.pdf</t>
+          <t>(a classificar)\0155_(a classificar)_09-10-2023_R$240,00_luis_f_monte_cipullo.pdf</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -6519,7 +6519,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2023-10-09</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -6538,7 +6538,7 @@
         </is>
       </c>
       <c r="F157" s="2" t="n">
-        <v>1200</v>
+        <v>240</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(a classificar)\0156_(a classificar)_13-10-2023_R$1.200,00_thiago_a_gomas_cunha.pdf</t>
+          <t>(a classificar)\0156_(a classificar)_09-10-2023_R$240,00_thiago_a_gomas_cunha.pdf</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -6558,12 +6558,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2023-10-09</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Felipe G Rosa</t>
+          <t>Andre Lima Monfrini</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="F158" s="2" t="n">
-        <v>1020</v>
+        <v>240</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(a classificar)\0157_(a classificar)_31-10-2023_R$1.020,00_felipe_g_rosa.pdf</t>
+          <t>(a classificar)\0157_(a classificar)_09-10-2023_R$240,00_andre_lima_monfrini.pdf</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -6597,12 +6597,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2023-10-09</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Luis F Monte Cipullo</t>
+          <t>Felipe G Rosa</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="F159" s="2" t="n">
-        <v>1020</v>
+        <v>240</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(a classificar)\0158_(a classificar)_31-10-2023_R$1.020,00_luis_f_monte_cipullo.pdf</t>
+          <t>(a classificar)\0158_(a classificar)_09-10-2023_R$240,00_felipe_g_rosa.pdf</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -6636,12 +6636,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2023-10-09</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Andre Lima Monfrini</t>
+          <t>Amir Labaki</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="F160" s="2" t="n">
-        <v>1020</v>
+        <v>945.49</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(a classificar)\0159_(a classificar)_31-10-2023_R$1.020,00_andre_lima_monfrini.pdf</t>
+          <t>(a classificar)\0159_(a classificar)_09-10-2023_R$945,49_amir_labaki.pdf</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -6675,12 +6675,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Bernardo T S Costa</t>
+          <t>Anne C Melo Santos</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -6694,7 +6694,7 @@
         </is>
       </c>
       <c r="F161" s="2" t="n">
-        <v>300</v>
+        <v>480</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(a classificar)\0160_(a classificar)_08-11-2023_R$300,00_bernardo_t_s_costa.pdf</t>
+          <t>(a classificar)\0160_(a classificar)_13-10-2023_R$480,00_anne_c_melo_santos.pdf</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -6714,34 +6714,38 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>GOL Linhas Aéreas (truncado)</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>Idalina S R Silva</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>11.400.274/0001-94</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
       <c r="F162" s="2" t="n">
-        <v>1524.64</v>
+        <v>480</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>AMBIGUO</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr"/>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>débito disputado por comprovantes: GOL LINHAS AEREAS</t>
-        </is>
-      </c>
+          <t>CONCILIADO</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>(a classificar)\0161_(a classificar)_13-10-2023_R$480,00_idalina_s_r_silva.pdf</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -6749,34 +6753,38 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>GOL Linhas Aéreas (truncado)</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr"/>
+          <t>Luis F Monte Cipullo</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>11.400.274/0001-94</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
       <c r="F163" s="2" t="n">
-        <v>1524.64</v>
+        <v>1200</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>AMBIGUO</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr"/>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>débito disputado por comprovantes: GOL LINHAS AEREAS</t>
-        </is>
-      </c>
+          <t>CONCILIADO</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>(a classificar)\0162_(a classificar)_13-10-2023_R$1.200,00_luis_f_monte_cipullo.pdf</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -6784,34 +6792,38 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>GOL Linhas Aéreas (truncado)</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
+          <t>Thiago A Gomas Cunha</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>11.400.274/0001-94</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
       <c r="F164" s="2" t="n">
-        <v>1524.64</v>
+        <v>1200</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>AMBIGUO</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr"/>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>débito disputado por comprovantes: GOL LINHAS AEREAS</t>
-        </is>
-      </c>
+          <t>CONCILIADO</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>(a classificar)\0163_(a classificar)_13-10-2023_R$1.200,00_thiago_a_gomas_cunha.pdf</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -6819,34 +6831,38 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>GOL Linhas Aéreas (truncado)</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr"/>
+          <t>Andre Lima Monfrini</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>11.400.274/0001-94</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
       <c r="F165" s="2" t="n">
-        <v>1524.64</v>
+        <v>1200</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>AMBIGUO</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr"/>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>débito disputado por comprovantes: GOL LINHAS AEREAS</t>
-        </is>
-      </c>
+          <t>CONCILIADO</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>(a classificar)\0164_(a classificar)_13-10-2023_R$1.200,00_andre_lima_monfrini.pdf</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -6854,34 +6870,38 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>GOL Linhas Aéreas (truncado)</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr"/>
+          <t>Felipe G Rosa</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>11.400.274/0001-94</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
       <c r="F166" s="2" t="n">
-        <v>2870.87</v>
+        <v>1200</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>AMBIGUO</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr"/>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>débito disputado por comprovantes: GOL LINHAS AEREAS</t>
-        </is>
-      </c>
+          <t>CONCILIADO</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>(a classificar)\0165_(a classificar)_13-10-2023_R$1.200,00_felipe_g_rosa.pdf</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -6889,34 +6909,38 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>GOL Linhas Aéreas (truncado)</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr"/>
+          <t>Camila Licariao de Carvalho Braune 4</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>36.584.511/0001-</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
       <c r="F167" s="2" t="n">
-        <v>2870.87</v>
+        <v>3000</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>AMBIGUO</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr"/>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>débito disputado por comprovantes: GOL LINHAS AEREAS</t>
-        </is>
-      </c>
+          <t>CONCILIADO</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>(a classificar)\0166_(a classificar)_16-10-2023_R$3.000,00_camila_licariao_de_carvalho_braune_4.pdf</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -6924,34 +6948,38 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>GOL Linhas Aéreas (truncado)</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr"/>
+          <t>Mog Produtora</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>11.400.274/0001-94</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
       <c r="F168" s="2" t="n">
-        <v>2870.87</v>
+        <v>10000</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>AMBIGUO</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr"/>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>débito disputado por comprovantes: GOL LINHAS AEREAS</t>
-        </is>
-      </c>
+          <t>CONCILIADO</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>(a classificar)\0167_(a classificar)_25-10-2023_R$10.000,00_mog_produtora.pdf</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -6959,34 +6987,38 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>GOL Linhas Aéreas (truncado)</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr"/>
+          <t>Luis F Monte Cipullo</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>11.400.274/0001-94</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
       <c r="F169" s="2" t="n">
-        <v>2870.87</v>
+        <v>1020</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>AMBIGUO</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>débito disputado por comprovantes: GOL LINHAS AEREAS</t>
-        </is>
-      </c>
+          <t>CONCILIADO</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>(a classificar)\0168_(a classificar)_31-10-2023_R$1.020,00_luis_f_monte_cipullo.pdf</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -6994,34 +7026,38 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2023-10-09</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>AMIR LABAKI (truncado)</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr"/>
+          <t>Andre Lima Monfrini</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>11.400.274/0001-94</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
       <c r="F170" s="2" t="n">
-        <v>945.49</v>
+        <v>1020</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>AMBIGUO</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr"/>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>débito disputado por comprovantes: AMIR LABAKI</t>
-        </is>
-      </c>
+          <t>CONCILIADO</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>(a classificar)\0169_(a classificar)_31-10-2023_R$1.020,00_andre_lima_monfrini.pdf</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -7029,34 +7065,38 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>CAMILA LICARIAO DE CARVALH (truncado)</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
+          <t>Felipe G Rosa</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>11.400.274/0001-94</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
       <c r="F171" s="2" t="n">
-        <v>3000</v>
+        <v>1020</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>AMBIGUO</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr"/>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>débito disputado por comprovantes: CAMILA LICARIAO DE CARVALHO BRAUNE 4</t>
-        </is>
-      </c>
+          <t>CONCILIADO</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>(a classificar)\0170_(a classificar)_31-10-2023_R$1.020,00_felipe_g_rosa.pdf</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -7064,34 +7104,38 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>MOG PRODUTORA (truncado)</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
+          <t>Bernardo T S Costa</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>11.400.274/0001-94</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
       <c r="F172" s="2" t="n">
-        <v>10000</v>
+        <v>300</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>AMBIGUO</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>débito disputado por comprovantes: MOG PRODUTORA</t>
-        </is>
-      </c>
+          <t>CONCILIADO</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>(a classificar)\0171_(a classificar)_08-11-2023_R$300,00_bernardo_t_s_costa.pdf</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -7104,10 +7148,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>MONICA GUIMARAES P MORAES (truncado)</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
+          <t>Monica G P Moraes</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>11.400.274/0001-94</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>(a classificar)</t>
@@ -7118,15 +7166,15 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>AMBIGUO</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr"/>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>débito disputado por comprovantes: MONICA G P MORAES</t>
-        </is>
-      </c>
+          <t>CONCILIADO</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>(a classificar)\0172_(a classificar)_14-11-2023_R$3.724,74_monica_g_p_moraes.pdf</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -7139,10 +7187,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>BANCO RENDIMENTO S/A (truncado)</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
+          <t>Banco Rendimento S/a</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>11.400.274/0001-94</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>(a classificar)</t>
@@ -7153,15 +7205,15 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>AMBIGUO</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr"/>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>débito disputado por comprovantes: BANCO RENDIMENTO S A</t>
-        </is>
-      </c>
+          <t>CONCILIADO</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>(a classificar)\0173_(a classificar)_03-02-2025_R$975,04_banco_rendimento_s_a.pdf</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -7169,32 +7221,40 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>BANCO RENDIMENTO S/A (truncado)</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
+          <t>Brilho</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>11.400.274/0001-94</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
       <c r="F175" s="2" t="n">
-        <v>975.04</v>
+        <v>211.5</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>AMBIGUO</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr"/>
+          <t>DIVERGENTE</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>PENDENTES\111 - 30-10-2023 - Brilho - Equipamento Luz (diária extra).pdf</t>
+        </is>
+      </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>débito disputado por comprovantes: BANCO RENDIMENTO S A</t>
+          <t>data bate (2023-10-30) mas valor diverge: extrato R$211.50 vs comprovante R$0.00</t>
         </is>
       </c>
     </row>
@@ -7204,40 +7264,32 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Gol Linhas Aéreas</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>11.400.274/0001-94</t>
-        </is>
-      </c>
+          <t>EDSON DE CAMARGO (truncado)</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
       <c r="F176" s="2" t="n">
-        <v>1524.64</v>
+        <v>700</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>AMBIGUO</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>(a classificar)\0175_(a classificar)_20-09-2023_R$1.524,64_gol_linhas_aereas.pdf</t>
-        </is>
-      </c>
+          <t>SEM-COMPROVANTE</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr">
         <is>
-          <t>comprovante disputado por débitos: GOL LINHAS AEREAS</t>
+          <t>comprovante do mesmo valor na data já vinculado a outro débito</t>
         </is>
       </c>
     </row>
@@ -7247,40 +7299,32 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Gol Linhas Aéreas</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>11.400.274/0001-94</t>
-        </is>
-      </c>
+          <t>Andre Lima Monfrini (truncado)</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
       <c r="F177" s="2" t="n">
-        <v>1524.64</v>
+        <v>500</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>AMBIGUO</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>(a classificar)\0176_(a classificar)_20-09-2023_R$1.524,64_gol_linhas_aereas.pdf</t>
-        </is>
-      </c>
+          <t>SEM-COMPROVANTE</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr">
         <is>
-          <t>comprovante disputado por débitos: GOL LINHAS AEREAS</t>
+          <t>data/valor não bate</t>
         </is>
       </c>
     </row>
@@ -7290,40 +7334,32 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Gol Linhas Aéreas</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>11.400.274/0001-94</t>
-        </is>
-      </c>
+          <t>BERNARDO TAVARES ROSA (truncado)</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
       <c r="F178" s="2" t="n">
-        <v>1524.64</v>
+        <v>300</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>AMBIGUO</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>(a classificar)\0177_(a classificar)_20-09-2023_R$1.524,64_gol_linhas_aereas.pdf</t>
-        </is>
-      </c>
+          <t>SEM-COMPROVANTE</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr">
         <is>
-          <t>comprovante disputado por débitos: GOL LINHAS AEREAS</t>
+          <t>comprovante do mesmo valor na data já vinculado a outro débito</t>
         </is>
       </c>
     </row>
@@ -7333,40 +7369,32 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Gol Linhas Aéreas</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>11.400.274/0001-94</t>
-        </is>
-      </c>
+          <t>LUIS FELIPE LABAKI (truncado)</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
       <c r="F179" s="2" t="n">
-        <v>1524.64</v>
+        <v>10000</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>AMBIGUO</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>(a classificar)\0178_(a classificar)_20-09-2023_R$1.524,64_gol_linhas_aereas.pdf</t>
-        </is>
-      </c>
+          <t>SEM-COMPROVANTE</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr">
         <is>
-          <t>comprovante disputado por débitos: GOL LINHAS AEREAS</t>
+          <t>data/valor não bate</t>
         </is>
       </c>
     </row>
@@ -7376,40 +7404,32 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Gol Linhas Aéreas</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>11.400.274/0001-94</t>
-        </is>
-      </c>
+          <t>ANA BEATRIZ HERMANSON POMA (truncado)</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
       <c r="F180" s="2" t="n">
-        <v>2870.87</v>
+        <v>3000</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>AMBIGUO</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>(a classificar)\0179_(a classificar)_20-09-2023_R$2.870,87_gol_linhas_aereas.pdf</t>
-        </is>
-      </c>
+          <t>SEM-COMPROVANTE</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr">
         <is>
-          <t>comprovante disputado por débitos: GOL LINHAS AEREAS</t>
+          <t>data/valor não bate</t>
         </is>
       </c>
     </row>
@@ -7419,40 +7439,32 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Gol Linhas Aéreas</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>11.400.274/0001-94</t>
-        </is>
-      </c>
+          <t>CIRCUNSTANC 1961 FSAMPJFN (truncado)</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
       <c r="F181" s="2" t="n">
-        <v>2870.87</v>
+        <v>975.04</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>AMBIGUO</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>(a classificar)\0180_(a classificar)_20-09-2023_R$2.870,87_gol_linhas_aereas.pdf</t>
-        </is>
-      </c>
+          <t>SEM-COMPROVANTE</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr">
         <is>
-          <t>comprovante disputado por débitos: GOL LINHAS AEREAS</t>
+          <t>comprovante do mesmo valor na data já vinculado a outro débito</t>
         </is>
       </c>
     </row>
@@ -7462,40 +7474,32 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Gol Linhas Aéreas</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>11.400.274/0001-94</t>
-        </is>
-      </c>
+          <t>BANCO RENDIMENTO S/A (truncado)</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
       <c r="F182" s="2" t="n">
-        <v>2870.87</v>
+        <v>975.04</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>AMBIGUO</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>(a classificar)\0181_(a classificar)_20-09-2023_R$2.870,87_gol_linhas_aereas.pdf</t>
-        </is>
-      </c>
+          <t>SEM-COMPROVANTE</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr">
         <is>
-          <t>comprovante disputado por débitos: GOL LINHAS AEREAS</t>
+          <t>comprovante do mesmo valor na data já vinculado a outro débito</t>
         </is>
       </c>
     </row>
@@ -7505,12 +7509,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-10-09</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Gol Linhas Aéreas</t>
+          <t>Amir Labaki</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -7524,21 +7528,21 @@
         </is>
       </c>
       <c r="F183" s="2" t="n">
-        <v>2870.87</v>
+        <v>945.49</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>AMBIGUO</t>
+          <t>SEM-EXTRATO</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(a classificar)\0182_(a classificar)_20-09-2023_R$2.870,87_gol_linhas_aereas.pdf</t>
+          <t>(a classificar)\0182_(a classificar)_09-10-2023_R$945,49_amir_labaki.pdf</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>comprovante disputado por débitos: GOL LINHAS AEREAS</t>
+          <t>sem débito correspondente</t>
         </is>
       </c>
     </row>
@@ -7548,17 +7552,17 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2023-10-09</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Amir Labaki</t>
+          <t>Camila Licariao de Carvalho Braune 4</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>36.584.511/0001-</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -7567,21 +7571,21 @@
         </is>
       </c>
       <c r="F184" s="2" t="n">
-        <v>945.49</v>
+        <v>3000</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>AMBIGUO</t>
+          <t>SEM-EXTRATO</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(a classificar)\0183_(a classificar)_09-10-2023_R$945,49_amir_labaki.pdf</t>
+          <t>(a classificar)\0183_(a classificar)_16-10-2023_R$3.000,00_camila_licariao_de_carvalho_braune_4.pdf</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>comprovante disputado por débitos: AMIR LABAKI</t>
+          <t>sem débito correspondente</t>
         </is>
       </c>
     </row>
@@ -7591,12 +7595,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2023-10-09</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Amir Labaki</t>
+          <t>Mog Produtora</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -7610,21 +7614,21 @@
         </is>
       </c>
       <c r="F185" s="2" t="n">
-        <v>945.49</v>
+        <v>10000</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>AMBIGUO</t>
+          <t>SEM-EXTRATO</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(a classificar)\0184_(a classificar)_09-10-2023_R$945,49_amir_labaki.pdf</t>
+          <t>(a classificar)\0184_(a classificar)_25-10-2023_R$10.000,00_mog_produtora.pdf</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>comprovante disputado por débitos: AMIR LABAKI</t>
+          <t>sem débito correspondente</t>
         </is>
       </c>
     </row>
@@ -7634,17 +7638,17 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Camila Licariao de Carvalho Braune 4</t>
+          <t>Monica G P Moraes</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>36.584.511/0001-</t>
+          <t>11.400.274/0001-94</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -7653,537 +7657,26 @@
         </is>
       </c>
       <c r="F186" s="2" t="n">
-        <v>3000</v>
+        <v>3724.74</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>AMBIGUO</t>
+          <t>SEM-EXTRATO</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(a classificar)\0185_(a classificar)_16-10-2023_R$3.000,00_camila_licariao_de_carvalho_braune_4.pdf</t>
+          <t>(a classificar)\0185_(a classificar)_14-11-2023_R$3.724,74_monica_g_p_moraes.pdf</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>comprovante disputado por débitos: CAMILA LICARIAO DE CARVALH</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="n">
-        <v>186</v>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>2023-10-16</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Camila Licariao de Carvalho Braune 4</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>36.584.511/0001-</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>(a classificar)</t>
-        </is>
-      </c>
-      <c r="F187" s="2" t="n">
-        <v>3000</v>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>AMBIGUO</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>(a classificar)\0186_(a classificar)_16-10-2023_R$3.000,00_camila_licariao_de_carvalho_braune_4.pdf</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>comprovante disputado por débitos: CAMILA LICARIAO DE CARVALH</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="n">
-        <v>187</v>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Mog Produtora</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>11.400.274/0001-94</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>(a classificar)</t>
-        </is>
-      </c>
-      <c r="F188" s="2" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>AMBIGUO</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>(a classificar)\0187_(a classificar)_25-10-2023_R$10.000,00_mog_produtora.pdf</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>comprovante disputado por débitos: MOG PRODUTORA</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="n">
-        <v>188</v>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Mog Produtora</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>11.400.274/0001-94</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>(a classificar)</t>
-        </is>
-      </c>
-      <c r="F189" s="2" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>AMBIGUO</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>(a classificar)\0188_(a classificar)_25-10-2023_R$10.000,00_mog_produtora.pdf</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>comprovante disputado por débitos: MOG PRODUTORA</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="n">
-        <v>189</v>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>2023-11-14</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Monica G P Moraes</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>11.400.274/0001-94</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>(a classificar)</t>
-        </is>
-      </c>
-      <c r="F190" s="2" t="n">
-        <v>3724.74</v>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>AMBIGUO</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>(a classificar)\0189_(a classificar)_14-11-2023_R$3.724,74_monica_g_p_moraes.pdf</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>comprovante disputado por débitos: MONICA GUIMARAES P MORAES</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="n">
-        <v>190</v>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>2023-11-14</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Monica G P Moraes</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>11.400.274/0001-94</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>(a classificar)</t>
-        </is>
-      </c>
-      <c r="F191" s="2" t="n">
-        <v>3724.74</v>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>AMBIGUO</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>(a classificar)\0190_(a classificar)_14-11-2023_R$3.724,74_monica_g_p_moraes.pdf</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>comprovante disputado por débitos: MONICA GUIMARAES P MORAES</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="n">
-        <v>191</v>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>2025-02-03</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Banco Rendimento S/a</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>11.400.274/0001-94</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>(a classificar)</t>
-        </is>
-      </c>
-      <c r="F192" s="2" t="n">
-        <v>975.04</v>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>AMBIGUO</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>(a classificar)\0191_(a classificar)_03-02-2025_R$975,04_banco_rendimento_s_a.pdf</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>comprovante disputado por débitos: BANCO RENDIMENTO S A</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="n">
-        <v>192</v>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>2023-10-30</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>Brilho</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>11.400.274/0001-94</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>(a classificar)</t>
-        </is>
-      </c>
-      <c r="F193" s="2" t="n">
-        <v>211.5</v>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>DIVERGENTE</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>PENDENTES\111 - 30-10-2023 - Brilho - Equipamento Luz (diária extra).pdf</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>data bate (2023-10-30) mas valor diverge: extrato R$211.50 vs comprovante R$0.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="n">
-        <v>193</v>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>2023-10-05</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>EDSON DE CAMARGO (truncado)</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr"/>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>(a classificar)</t>
-        </is>
-      </c>
-      <c r="F194" s="2" t="n">
-        <v>700</v>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>SEM-COMPROVANTE</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr"/>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>comprovante do mesmo valor na data já vinculado a outro débito</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="n">
-        <v>194</v>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>2023-10-10</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>Andre Lima Monfrini (truncado)</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr"/>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>(a classificar)</t>
-        </is>
-      </c>
-      <c r="F195" s="2" t="n">
-        <v>500</v>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>SEM-COMPROVANTE</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr"/>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>data/valor não bate</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="n">
-        <v>195</v>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>2023-11-08</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>BERNARDO TAVARES ROSA (truncado)</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr"/>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>(a classificar)</t>
-        </is>
-      </c>
-      <c r="F196" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>SEM-COMPROVANTE</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>comprovante do mesmo valor na data já vinculado a outro débito</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="n">
-        <v>196</v>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>2023-09-26</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>LUIS FELIPE LABAKI (truncado)</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr"/>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>(a classificar)</t>
-        </is>
-      </c>
-      <c r="F197" s="2" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>SEM-COMPROVANTE</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr"/>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>data/valor não bate</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="n">
-        <v>197</v>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>2023-09-26</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>ANA BEATRIZ HERMANSON POMA (truncado)</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr"/>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>(a classificar)</t>
-        </is>
-      </c>
-      <c r="F198" s="2" t="n">
-        <v>3000</v>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>SEM-COMPROVANTE</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr"/>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>data/valor não bate</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="n">
-        <v>198</v>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>2025-02-03</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>CIRCUNSTANC 1961 FSAMPJFN (truncado)</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr"/>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>(a classificar)</t>
-        </is>
-      </c>
-      <c r="F199" s="2" t="n">
-        <v>975.04</v>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>SEM-COMPROVANTE</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr"/>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>comprovante do mesmo valor na data já vinculado a outro débito</t>
+          <t>sem débito correspondente</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I199"/>
+  <autoFilter ref="A1:I186"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida/planilha/planilha_corrigida.xlsx
+++ b/saida/planilha/planilha_corrigida.xlsx
@@ -40,7 +40,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -56,11 +56,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,12 +434,12 @@
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="62" customWidth="1" min="8" max="8"/>
-    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -492,7 +493,7 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>2022-11-04</t>
         </is>
@@ -504,7 +505,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (1 de 143)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -512,8 +513,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
-        <v>5000</v>
+      <c r="F2" s="3" t="n">
+        <v>11000</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -522,7 +523,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(a classificar)\0001_(a classificar)_04-11-2022_R$5.000,00_circunstancia_cinematografica_e_prod.pdf</t>
+          <t>001_a-classificar_04-11-2022_R$11.000,00_circunstancia-cinematografica-e-prod.pdf</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -531,7 +532,7 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>2022-11-04</t>
         </is>
@@ -543,7 +544,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (2 de 143)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -551,8 +552,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n">
-        <v>11000</v>
+      <c r="F3" s="3" t="n">
+        <v>30000</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -561,7 +562,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(a classificar)\0002_(a classificar)_04-11-2022_R$11.000,00_circunstancia_cinematografica_e_prod.pdf</t>
+          <t>002_a-classificar_04-11-2022_R$30.000,00_circunstancia-cinematografica-e-prod.pdf</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -570,7 +571,7 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>2022-11-04</t>
         </is>
@@ -582,7 +583,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (3 de 143)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -590,7 +591,7 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="3" t="n">
         <v>20000</v>
       </c>
       <c r="G4" t="inlineStr">
@@ -600,7 +601,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(a classificar)\0003_(a classificar)_04-11-2022_R$20.000,00_circunstancia_cinematografica_e_prod.pdf</t>
+          <t>003_a-classificar_04-11-2022_R$20.000,00_circunstancia-cinematografica-e-prod.pdf</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -609,7 +610,7 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>2022-11-04</t>
         </is>
@@ -621,7 +622,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (4 de 143)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -629,8 +630,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n">
-        <v>30000</v>
+      <c r="F5" s="3" t="n">
+        <v>5000</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -639,7 +640,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(a classificar)\0004_(a classificar)_04-11-2022_R$30.000,00_circunstancia_cinematografica_e_prod.pdf</t>
+          <t>004_a-classificar_04-11-2022_R$5.000,00_circunstancia-cinematografica-e-prod.pdf</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -648,19 +649,19 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2022-11-21</t>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2022-11-10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Luis F Monte Cipullo</t>
+          <t>Felipe G Rosa</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>442.561.298-12</t>
+          <t>11.400.274/0001-94 (5 de 143)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -668,8 +669,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n">
-        <v>800</v>
+      <c r="F6" s="3" t="n">
+        <v>1200</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -678,7 +679,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(a classificar)\0005_(a classificar)_21-11-2022_R$800,00_luis_f_monte_cipullo.pdf</t>
+          <t>005_a-classificar_10-11-2022_R$1.200,00_felipe-g-rosa.pdf</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -687,19 +688,19 @@
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2022-11-28</t>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>2022-11-10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Circunstancia Cinematografica e Prod</t>
+          <t>Luis Felipe Labaki</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (6 de 143)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -707,8 +708,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F7" s="2" t="n">
-        <v>20000</v>
+      <c r="F7" s="3" t="n">
+        <v>1200</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -717,7 +718,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(a classificar)\0006_(a classificar)_28-11-2022_R$20.000,00_circunstancia_cinematografica_e_prod.pdf</t>
+          <t>006_a-classificar_10-11-2022_R$1.200,00_luis-felipe-labaki.pdf</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -726,19 +727,19 @@
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2022-12-12</t>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2022-11-21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Circunstancia Cinematografica e Prod</t>
+          <t>Luis F Monte Cipullo</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>442.561.298-12</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -746,8 +747,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F8" s="2" t="n">
-        <v>30000</v>
+      <c r="F8" s="3" t="n">
+        <v>800</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -756,7 +757,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(a classificar)\0007_(a classificar)_12-12-2022_R$30.000,00_circunstancia_cinematografica_e_prod.pdf</t>
+          <t>007_a-classificar_21-11-2022_R$800,00_luis-f-monte-cipullo.pdf</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -765,19 +766,19 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2022-12-14</t>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2022-11-28</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Planifilmes Ltda</t>
+          <t>Circunstancia Cinematografica e Prod</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (7 de 143)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -785,8 +786,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F9" s="2" t="n">
-        <v>2000</v>
+      <c r="F9" s="3" t="n">
+        <v>20000</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -795,7 +796,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(a classificar)\0008_(a classificar)_14-12-2022_R$2.000,00_planifilmes_ltda.pdf</t>
+          <t>008_a-classificar_28-11-2022_R$20.000,00_circunstancia-cinematografica-e-prod.pdf</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -804,19 +805,19 @@
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2022-12-14</t>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2022-12-12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Julia Barbara Melo de Sousa 40926175</t>
+          <t>Circunstancia Cinematografica e Prod</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (8 de 143)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -824,8 +825,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F10" s="2" t="n">
-        <v>6000</v>
+      <c r="F10" s="3" t="n">
+        <v>30000</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -834,7 +835,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(a classificar)\0009_(a classificar)_14-12-2022_R$6.000,00_julia_barbara_melo_de_sousa_40926175.pdf</t>
+          <t>009_a-classificar_12-12-2022_R$30.000,00_circunstancia-cinematografica-e-prod.pdf</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -843,19 +844,19 @@
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2022-12-20</t>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>2022-12-14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Circunstancia Cinematografica e Prod</t>
+          <t>Julia Barbara Melo de Sousa 40926175</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (9 de 143)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -863,8 +864,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F11" s="2" t="n">
-        <v>20000</v>
+      <c r="F11" s="3" t="n">
+        <v>6000</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -873,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(a classificar)\0010_(a classificar)_20-12-2022_R$20.000,00_circunstancia_cinematografica_e_prod.pdf</t>
+          <t>010_a-classificar_14-12-2022_R$6.000,00_julia-barbara-melo-de-sousa-40926175.pdf</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -882,19 +883,19 @@
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2023-01-23</t>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2022-12-14</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Circunstancia Cinematografica e Prod</t>
+          <t>Planifilmes Ltda</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (10 de 143)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -902,8 +903,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F12" s="2" t="n">
-        <v>4500</v>
+      <c r="F12" s="3" t="n">
+        <v>2000</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -912,7 +913,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(a classificar)\0011_(a classificar)_23-01-2023_R$4.500,00_circunstancia_cinematografica_e_prod.pdf</t>
+          <t>011_a-classificar_14-12-2022_R$2.000,00_planifilmes-ltda.pdf</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -921,9 +922,9 @@
       <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2023-01-23</t>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2022-12-20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -933,7 +934,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (11 de 143)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -941,8 +942,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F13" s="2" t="n">
-        <v>30000</v>
+      <c r="F13" s="3" t="n">
+        <v>20000</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -951,7 +952,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(a classificar)\0012_(a classificar)_23-01-2023_R$30.000,00_circunstancia_cinematografica_e_prod.pdf</t>
+          <t>012_a-classificar_20-12-2022_R$20.000,00_circunstancia-cinematografica-e-prod.pdf</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -960,9 +961,9 @@
       <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2023-02-22</t>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -972,7 +973,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (12 de 143)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -980,8 +981,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F14" s="2" t="n">
-        <v>19550</v>
+      <c r="F14" s="3" t="n">
+        <v>30000</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -990,7 +991,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(a classificar)\0013_(a classificar)_22-02-2023_R$19.550,00_circunstancia_cinematografica_e_prod.pdf</t>
+          <t>013_a-classificar_23-01-2023_R$30.000,00_circunstancia-cinematografica-e-prod.pdf</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -999,19 +1000,19 @@
       <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2023-08-18</t>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Radio e Televisao Bandeirantes S.a.</t>
+          <t>Circunstancia Cinematografica e Prod</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (13 de 143)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1019,8 +1020,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F15" s="2" t="n">
-        <v>380</v>
+      <c r="F15" s="3" t="n">
+        <v>4500</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1029,7 +1030,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(a classificar)\0014_(a classificar)_18-08-2023_R$380,00_radio_e_televisao_bandeirantes_s_a.pdf</t>
+          <t>014_a-classificar_23-01-2023_R$4.500,00_circunstancia-cinematografica-e-prod.pdf</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1038,19 +1039,19 @@
       <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2023-08-25</t>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>2023-02-22</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Memoria Coletiva Imagens e Textos Lt</t>
+          <t>Circunstancia Cinematografica e Prod</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (14 de 143)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1058,8 +1059,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F16" s="2" t="n">
-        <v>10500</v>
+      <c r="F16" s="3" t="n">
+        <v>19550</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1068,7 +1069,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(a classificar)\0015_(a classificar)_25-08-2023_R$10.500,00_memoria_coletiva_imagens_e_textos_lt.pdf</t>
+          <t>015_a-classificar_22-02-2023_R$19.550,00_circunstancia-cinematografica-e-prod.pdf</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -1077,19 +1078,19 @@
       <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2023-09-04</t>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>2023-07-03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Porviroscopio Projetos C. C. Ltda</t>
+          <t>Circunstancia Cinematografica e Prod</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (15 de 143)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1097,8 +1098,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F17" s="2" t="n">
-        <v>700</v>
+      <c r="F17" s="3" t="n">
+        <v>25000</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1107,7 +1108,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(a classificar)\0016_(a classificar)_04-09-2023_R$700,00_porviroscopio_projetos_c_c_ltda.pdf</t>
+          <t>016_a-classificar_03-07-2023_R$25.000,00_circunstancia-cinematografica-e-prod.pdf</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -1116,19 +1117,19 @@
       <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2023-09-05</t>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>2023-07-03</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>:</t>
+          <t>Mog Produtora</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (16 de 143)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1136,8 +1137,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F18" s="2" t="n">
-        <v>120</v>
+      <c r="F18" s="3" t="n">
+        <v>25000</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1146,7 +1147,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(a classificar)\0017_(a classificar)_05-09-2023_R$120,00_sem_favorecido.pdf</t>
+          <t>017_a-classificar_03-07-2023_R$25.000,00_mog-produtora.pdf</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -1155,19 +1156,19 @@
       <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2023-09-05</t>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>2023-08-18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>favorecido</t>
+          <t>Radio e Televisao Bandeirantes S.a.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>05.111.581/0001-52</t>
+          <t>11.400.274/0001-94 (17 de 143)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1175,8 +1176,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F19" s="2" t="n">
-        <v>33000</v>
+      <c r="F19" s="3" t="n">
+        <v>380</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1185,7 +1186,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(a classificar)\0018_(a classificar)_05-09-2023_R$33.000,00_favorecido.pdf</t>
+          <t>018_a-classificar_18-08-2023_R$380,00_radio-e-televisao-bandeirantes-s-a.pdf</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -1194,19 +1195,19 @@
       <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2023-09-06</t>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Julia Barbara Melo de Sousa 40926175</t>
+          <t>Memoria Coletiva Imagens e Textos Lt</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (18 de 143)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1214,8 +1215,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F20" s="2" t="n">
-        <v>4900</v>
+      <c r="F20" s="3" t="n">
+        <v>10500</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1224,7 +1225,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(a classificar)\0019_(a classificar)_06-09-2023_R$4.900,00_julia_barbara_melo_de_sousa_40926175.pdf</t>
+          <t>019_a-classificar_25-08-2023_R$10.500,00_memoria-coletiva-imagens-e-textos-lt.pdf</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -1233,19 +1234,19 @@
       <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2023-09-11</t>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ana Beatriz Hermanson Pomar Servicos</t>
+          <t>Porviroscopio Projetos C. C. Ltda</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (19 de 143)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1253,8 +1254,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F21" s="2" t="n">
-        <v>3000</v>
+      <c r="F21" s="3" t="n">
+        <v>700</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1263,7 +1264,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(a classificar)\0020_(a classificar)_11-09-2023_R$3.000,00_ana_beatriz_hermanson_pomar_servicos.pdf</t>
+          <t>020_a-classificar_04-09-2023_R$700,00_porviroscopio-projetos-c-c-ltda.pdf</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -1272,19 +1273,19 @@
       <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2023-09-26</t>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Filmes de Taipa Prod</t>
+          <t>favorecido</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>05.111.581/0001-52</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1292,8 +1293,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F22" s="2" t="n">
-        <v>11250</v>
+      <c r="F22" s="3" t="n">
+        <v>33000</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1302,7 +1303,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(a classificar)\0021_(a classificar)_26-09-2023_R$11.250,00_filmes_de_taipa_prod.pdf</t>
+          <t>021_a-classificar_05-09-2023_R$33.000,00_favorecido.pdf</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -1311,19 +1312,19 @@
       <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2023-09-28</t>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Casa do Roadie</t>
+          <t>:</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (20 de 143)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1331,8 +1332,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F23" s="2" t="n">
-        <v>15.3</v>
+      <c r="F23" s="3" t="n">
+        <v>120</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1341,7 +1342,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(a classificar)\0022_(a classificar)_28-09-2023_R$15,30_casa_do_roadie.pdf</t>
+          <t>022_a-classificar_05-09-2023_R$120,00_sem-nome.pdf</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -1350,19 +1351,19 @@
       <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2023-09-28</t>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Casa do Roadie</t>
+          <t>Julia Barbara Melo de Sousa 40926175</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (21 de 143)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1370,8 +1371,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F24" s="2" t="n">
-        <v>350</v>
+      <c r="F24" s="3" t="n">
+        <v>4900</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1380,7 +1381,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(a classificar)\0023_(a classificar)_28-09-2023_R$350,00_casa_do_roadie.pdf</t>
+          <t>023_a-classificar_06-09-2023_R$4.900,00_julia-barbara-melo-de-sousa-40926175.pdf</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -1389,19 +1390,19 @@
       <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2023-09-28</t>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cityhome Servicos Imobiliarios Ltda</t>
+          <t>Ana Beatriz Hermanson Pomar Servicos</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (22 de 143)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1409,8 +1410,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F25" s="2" t="n">
-        <v>8800</v>
+      <c r="F25" s="3" t="n">
+        <v>3000</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1419,7 +1420,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(a classificar)\0024_(a classificar)_28-09-2023_R$8.800,00_cityhome_servicos_imobiliarios_ltda.pdf</t>
+          <t>024_a-classificar_11-09-2023_R$3.000,00_ana-beatriz-hermanson-pomar-servicos.pdf</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -1428,19 +1429,19 @@
       <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2023-09-29</t>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scm Prest Serv Postais Ltda</t>
+          <t>Gol Linhas Aéreas</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (23 de 143)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1448,8 +1449,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F26" s="2" t="n">
-        <v>35.1</v>
+      <c r="F26" s="3" t="n">
+        <v>2870.87</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1458,7 +1459,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(a classificar)\0025_(a classificar)_29-09-2023_R$35,10_scm_prest_serv_postais_ltda.pdf</t>
+          <t>025_a-classificar_20-09-2023_R$2.870,87_gol-linhas-aereas.pdf</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -1467,19 +1468,19 @@
       <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2023-09-29</t>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cityhome Servicos Imobiliarios Ltda</t>
+          <t>Gol Linhas Aéreas</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (24 de 143)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1487,8 +1488,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F27" s="2" t="n">
-        <v>150</v>
+      <c r="F27" s="3" t="n">
+        <v>2870.87</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1497,7 +1498,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(a classificar)\0026_(a classificar)_29-09-2023_R$150,00_cityhome_servicos_imobiliarios_ltda.pdf</t>
+          <t>026_a-classificar_20-09-2023_R$2.870,87_gol-linhas-aereas.pdf</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -1506,19 +1507,19 @@
       <c r="A28" t="n">
         <v>27</v>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2023-09-29</t>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cityhome Servicos Imobiliarios Ltda</t>
+          <t>Gol Linhas Aéreas</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (25 de 143)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1526,8 +1527,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F28" s="2" t="n">
-        <v>500</v>
+      <c r="F28" s="3" t="n">
+        <v>2870.87</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1536,7 +1537,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(a classificar)\0027_(a classificar)_29-09-2023_R$500,00_cityhome_servicos_imobiliarios_ltda.pdf</t>
+          <t>027_a-classificar_20-09-2023_R$2.870,87_gol-linhas-aereas.pdf</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -1545,19 +1546,19 @@
       <c r="A29" t="n">
         <v>28</v>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2023-09-29</t>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Matron Informatica</t>
+          <t>Gol Linhas Aéreas</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>10.372.701/0001-05</t>
+          <t>11.400.274/0001-94 (26 de 143)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1565,8 +1566,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F29" s="2" t="n">
-        <v>3116</v>
+      <c r="F29" s="3" t="n">
+        <v>2870.87</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1575,7 +1576,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(a classificar)\0028_(a classificar)_29-09-2023_R$3.116,00_matron_informatica.pdf</t>
+          <t>028_a-classificar_20-09-2023_R$2.870,87_gol-linhas-aereas.pdf</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -1584,19 +1585,19 @@
       <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2023-09-29</t>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pateo Moinhos de Vento Adm e Part Lt</t>
+          <t>Gol Linhas Aéreas</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (27 de 143)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1604,8 +1605,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F30" s="2" t="n">
-        <v>5768.4</v>
+      <c r="F30" s="3" t="n">
+        <v>1524.64</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1614,7 +1615,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(a classificar)\0029_(a classificar)_29-09-2023_R$5.768,40_pateo_moinhos_de_vento_adm_e_part_lt.pdf</t>
+          <t>029_a-classificar_20-09-2023_R$1.524,64_gol-linhas-aereas.pdf</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -1623,19 +1624,19 @@
       <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2023-09-29</t>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Martina Milla Raffaelli Me</t>
+          <t>Gol Linhas Aéreas</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>09.466.037/0001-84</t>
+          <t>11.400.274/0001-94 (28 de 143)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1643,8 +1644,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F31" s="2" t="n">
-        <v>35000</v>
+      <c r="F31" s="3" t="n">
+        <v>1524.64</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1653,7 +1654,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(a classificar)\0030_(a classificar)_29-09-2023_R$35.000,00_martina_milla_raffaelli_me.pdf</t>
+          <t>030_a-classificar_20-09-2023_R$1.524,64_gol-linhas-aereas.pdf</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -1662,19 +1663,19 @@
       <c r="A32" t="n">
         <v>31</v>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2023-10-02</t>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pateo Moinhos de Vento Adm e Part Lt</t>
+          <t>Gol Linhas Aéreas</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (29 de 143)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1682,8 +1683,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F32" s="2" t="n">
-        <v>1610</v>
+      <c r="F32" s="3" t="n">
+        <v>1524.64</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1692,7 +1693,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(a classificar)\0031_(a classificar)_02-10-2023_R$1.610,00_pateo_moinhos_de_vento_adm_e_part_lt.pdf</t>
+          <t>031_a-classificar_20-09-2023_R$1.524,64_gol-linhas-aereas.pdf</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -1701,19 +1702,19 @@
       <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2023-10-03</t>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Glademir M Machado</t>
+          <t>Gol Linhas Aéreas</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (30 de 143)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1721,8 +1722,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F33" s="2" t="n">
-        <v>200</v>
+      <c r="F33" s="3" t="n">
+        <v>1524.64</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1731,7 +1732,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(a classificar)\0032_(a classificar)_03-10-2023_R$200,00_glademir_m_machado.pdf</t>
+          <t>032_a-classificar_20-09-2023_R$1.524,64_gol-linhas-aereas.pdf</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -1740,97 +1741,89 @@
       <c r="A34" t="n">
         <v>33</v>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2023-10-03</t>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Matron Informatica</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>10.372.701/0001-05</t>
-        </is>
-      </c>
+          <t>ANA BEATRIZ HERMANSON POMA (truncado)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F34" s="2" t="n">
-        <v>3020</v>
+      <c r="F34" s="3" t="n">
+        <v>3000</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>CONCILIADO</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(a classificar)\0033_(a classificar)_03-10-2023_R$3.020,00_matron_informatica.pdf</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>SEM-COMPROVANTE</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>débito no extrato sem comprovante correspondente</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>34</v>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2023-10-05</t>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Amir Labaki</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>11.400.274/0001-94</t>
-        </is>
-      </c>
+          <t>LUIS FELIPE LABAKI (truncado)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F35" s="2" t="n">
-        <v>500</v>
+      <c r="F35" s="3" t="n">
+        <v>10000</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>CONCILIADO</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(a classificar)\0034_(a classificar)_05-10-2023_R$500,00_amir_labaki.pdf</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>SEM-COMPROVANTE</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>débito no extrato sem comprovante correspondente</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>35</v>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2023-10-06</t>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Memoria Coletiva Imagens e Textos Lt</t>
+          <t>Filmes de Taipa Prod</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (31 de 143)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1838,8 +1831,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F36" s="2" t="n">
-        <v>10500</v>
+      <c r="F36" s="3" t="n">
+        <v>11250</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1848,7 +1841,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(a classificar)\0035_(a classificar)_06-10-2023_R$10.500,00_memoria_coletiva_imagens_e_textos_lt.pdf</t>
+          <t>035_a-classificar_26-09-2023_R$11.250,00_filmes-de-taipa-prod.pdf</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -1857,19 +1850,19 @@
       <c r="A37" t="n">
         <v>36</v>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2023-10-09</t>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Fabio Baltar Duarte</t>
+          <t>Casa do Roadie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (32 de 143)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1877,8 +1870,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F37" s="2" t="n">
-        <v>1800</v>
+      <c r="F37" s="3" t="n">
+        <v>350</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1887,7 +1880,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(a classificar)\0036_(a classificar)_09-10-2023_R$1.800,00_fabio_baltar_duarte.pdf</t>
+          <t>036_a-classificar_28-09-2023_R$350,00_casa-do-roadie.pdf</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -1896,19 +1889,19 @@
       <c r="A38" t="n">
         <v>37</v>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2023-10-09</t>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Fabio Baltar Duarte</t>
+          <t>Sofia V Baccarini</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (33 de 143)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1916,8 +1909,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F38" s="2" t="n">
-        <v>1800.01</v>
+      <c r="F38" s="3" t="n">
+        <v>1000</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1926,7 +1919,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(a classificar)\0037_(a classificar)_09-10-2023_R$1.800,01_fabio_baltar_duarte.pdf</t>
+          <t>037_a-classificar_28-09-2023_R$1.000,00_sofia-v-baccarini.pdf</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -1935,19 +1928,19 @@
       <c r="A39" t="n">
         <v>38</v>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2023-10-09</t>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thiago Augusto Gomas Cunha 397893948</t>
+          <t>Andre Lima Manfrim</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (34 de 143)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1955,8 +1948,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F39" s="2" t="n">
-        <v>4800</v>
+      <c r="F39" s="3" t="n">
+        <v>1000</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1965,7 +1958,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(a classificar)\0038_(a classificar)_09-10-2023_R$4.800,00_thiago_augusto_gomas_cunha_397893948.pdf</t>
+          <t>038_a-classificar_28-09-2023_R$1.000,00_andre-lima-manfrim.pdf</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -1974,19 +1967,19 @@
       <c r="A40" t="n">
         <v>39</v>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2023-10-09</t>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Luis Felipe Monte Cipullo 4425612981</t>
+          <t>Casa do Roadie</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>22.592.616/0001-31</t>
+          <t>11.400.274/0001-94 (35 de 143)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1994,8 +1987,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F40" s="2" t="n">
-        <v>7500</v>
+      <c r="F40" s="3" t="n">
+        <v>15.3</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2004,7 +1997,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(a classificar)\0039_(a classificar)_09-10-2023_R$7.500,00_luis_felipe_monte_cipullo_4425612981.pdf</t>
+          <t>039_a-classificar_28-09-2023_R$15,30_casa-do-roadie.pdf</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -2013,19 +2006,19 @@
       <c r="A41" t="n">
         <v>40</v>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2023-10-09</t>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Mandala Tours</t>
+          <t>Cityhome Servicos Imobiliarios Ltda</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (36 de 143)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2033,8 +2026,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F41" s="2" t="n">
-        <v>9502.77</v>
+      <c r="F41" s="3" t="n">
+        <v>8800</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2043,7 +2036,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(a classificar)\0040_(a classificar)_09-10-2023_R$9.502,77_mandala_tours.pdf</t>
+          <t>040_a-classificar_28-09-2023_R$8.800,00_cityhome-servicos-imobiliarios-ltda.pdf</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -2052,19 +2045,19 @@
       <c r="A42" t="n">
         <v>41</v>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2023-10-09</t>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Mog Produtora</t>
+          <t>Pateo Moinhos de Vento Adm e Part Lt</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (37 de 143)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2072,8 +2065,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F42" s="2" t="n">
-        <v>13500</v>
+      <c r="F42" s="3" t="n">
+        <v>5768.4</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2082,7 +2075,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(a classificar)\0041_(a classificar)_09-10-2023_R$13.500,00_mog_produtora.pdf</t>
+          <t>041_a-classificar_29-09-2023_R$5.768,40_pateo-moinhos-de-vento-adm-e-part-lt.pdf</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -2091,19 +2084,19 @@
       <c r="A43" t="n">
         <v>42</v>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2023-10-10</t>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Faculdade de Arquitetura e Urbanismo</t>
+          <t>Cityhome Servicos Imobiliarios Ltda</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (38 de 143)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2111,8 +2104,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F43" s="2" t="n">
-        <v>2300</v>
+      <c r="F43" s="3" t="n">
+        <v>500</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2121,7 +2114,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(a classificar)\0042_(a classificar)_10-10-2023_R$2.300,00_faculdade_de_arquitetura_e_urbanismo.pdf</t>
+          <t>042_a-classificar_29-09-2023_R$500,00_cityhome-servicos-imobiliarios-ltda.pdf</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -2130,19 +2123,19 @@
       <c r="A44" t="n">
         <v>43</v>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2023-10-11</t>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Aamac</t>
+          <t>Martina Milla Raffaelli Me</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>09.466.037/0001-84</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2150,8 +2143,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F44" s="2" t="n">
-        <v>400</v>
+      <c r="F44" s="3" t="n">
+        <v>35000</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2160,7 +2153,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(a classificar)\0043_(a classificar)_11-10-2023_R$400,00_aamac.pdf</t>
+          <t>043_a-classificar_29-09-2023_R$35.000,00_martina-milla-raffaelli-me.pdf</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -2169,19 +2162,19 @@
       <c r="A45" t="n">
         <v>44</v>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2023-10-11</t>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Malnes Transporte e Produção</t>
+          <t>Matron Informatica</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>10.372.701/0001-05 (1 de 2)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2189,8 +2182,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F45" s="2" t="n">
-        <v>500</v>
+      <c r="F45" s="3" t="n">
+        <v>3116</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2199,7 +2192,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(a classificar)\0044_(a classificar)_11-10-2023_R$500,00_malnes_transporte_e_producao.pdf</t>
+          <t>044_a-classificar_29-09-2023_R$3.116,00_matron-informatica.pdf</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -2208,19 +2201,19 @@
       <c r="A46" t="n">
         <v>45</v>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2023-10-11</t>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Idalina S R Silva</t>
+          <t>Luis F Monte Cipullo</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (39 de 143)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2228,8 +2221,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F46" s="2" t="n">
-        <v>1000</v>
+      <c r="F46" s="3" t="n">
+        <v>1050</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2238,7 +2231,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(a classificar)\0045_(a classificar)_11-10-2023_R$1.000,00_idalina_s_r_silva.pdf</t>
+          <t>045_a-classificar_29-09-2023_R$1.050,00_luis-f-monte-cipullo.pdf</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -2247,19 +2240,19 @@
       <c r="A47" t="n">
         <v>46</v>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2023-10-11</t>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ana Beatriz Hermanson Pomar Servicos</t>
+          <t>Felipe G Rosa</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (40 de 143)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2267,8 +2260,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F47" s="2" t="n">
-        <v>1500</v>
+      <c r="F47" s="3" t="n">
+        <v>1050</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2277,7 +2270,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(a classificar)\0046_(a classificar)_11-10-2023_R$1.500,00_ana_beatriz_hermanson_pomar_servicos.pdf</t>
+          <t>046_a-classificar_29-09-2023_R$1.050,00_felipe-g-rosa.pdf</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -2286,19 +2279,19 @@
       <c r="A48" t="n">
         <v>47</v>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2023-10-11</t>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Vondoc Filmes Ltda</t>
+          <t>Thiago A Gomas Cunha</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (41 de 143)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2306,8 +2299,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F48" s="2" t="n">
-        <v>4000</v>
+      <c r="F48" s="3" t="n">
+        <v>1050</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2316,7 +2309,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(a classificar)\0047_(a classificar)_11-10-2023_R$4.000,00_vondoc_filmes_ltda.pdf</t>
+          <t>047_a-classificar_29-09-2023_R$1.050,00_thiago-a-gomas-cunha.pdf</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -2325,19 +2318,19 @@
       <c r="A49" t="n">
         <v>48</v>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2023-10-11</t>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Mandala Tours</t>
+          <t>Sofia V Baccarini</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (42 de 143)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2345,8 +2338,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F49" s="2" t="n">
-        <v>9672</v>
+      <c r="F49" s="3" t="n">
+        <v>560</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2355,7 +2348,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(a classificar)\0048_(a classificar)_11-10-2023_R$9.672,00_mandala_tours.pdf</t>
+          <t>048_a-classificar_29-09-2023_R$560,00_sofia-v-baccarini.pdf</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -2364,19 +2357,19 @@
       <c r="A50" t="n">
         <v>49</v>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2023-10-13</t>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ricardo Dias Santos</t>
+          <t>Fabio Baltar Duarte</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (43 de 143)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2384,8 +2377,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F50" s="2" t="n">
-        <v>300</v>
+      <c r="F50" s="3" t="n">
+        <v>560</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2394,7 +2387,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(a classificar)\0049_(a classificar)_13-10-2023_R$300,00_ricardo_dias_santos.pdf</t>
+          <t>049_a-classificar_29-09-2023_R$560,00_fabio-baltar-duarte.pdf</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -2403,19 +2396,19 @@
       <c r="A51" t="n">
         <v>50</v>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2023-10-13</t>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Andre Lima Manfrim</t>
+          <t>Andre Lima Monfrini</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (44 de 143)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2423,8 +2416,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F51" s="2" t="n">
-        <v>1000</v>
+      <c r="F51" s="3" t="n">
+        <v>1050</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2433,7 +2426,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(a classificar)\0050_(a classificar)_13-10-2023_R$1.000,00_andre_lima_manfrim.pdf</t>
+          <t>050_a-classificar_29-09-2023_R$1.050,00_andre-lima-monfrini.pdf</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -2442,19 +2435,19 @@
       <c r="A52" t="n">
         <v>51</v>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2023-10-13</t>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Maga Projetos Culturais</t>
+          <t>Cityhome Servicos Imobiliarios Ltda</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (45 de 143)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2462,8 +2455,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F52" s="2" t="n">
-        <v>2000</v>
+      <c r="F52" s="3" t="n">
+        <v>150</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2472,7 +2465,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(a classificar)\0051_(a classificar)_13-10-2023_R$2.000,00_maga_projetos_culturais.pdf</t>
+          <t>051_a-classificar_29-09-2023_R$150,00_cityhome-servicos-imobiliarios-ltda.pdf</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -2481,19 +2474,19 @@
       <c r="A53" t="n">
         <v>52</v>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2023-10-16</t>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Luz Rio Locacao de Equipamentos Cine</t>
+          <t>Scm Prest Serv Postais Ltda</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (46 de 143)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2501,8 +2494,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F53" s="2" t="n">
-        <v>1100</v>
+      <c r="F53" s="3" t="n">
+        <v>35.1</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2511,7 +2504,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(a classificar)\0052_(a classificar)_16-10-2023_R$1.100,00_luz_rio_locacao_de_equipamentos_cine.pdf</t>
+          <t>052_a-classificar_29-09-2023_R$35,10_scm-prest-serv-postais-ltda.pdf</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -2520,19 +2513,19 @@
       <c r="A54" t="n">
         <v>53</v>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2023-10-17</t>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cristhiano Rodrigues de Jesus 041338</t>
+          <t>Pateo Moinhos de Vento Adm e Part Lt</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (47 de 143)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2540,8 +2533,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F54" s="2" t="n">
-        <v>4375</v>
+      <c r="F54" s="3" t="n">
+        <v>1610</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2550,7 +2543,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(a classificar)\0053_(a classificar)_17-10-2023_R$4.375,00_cristhiano_rodrigues_de_jesus_041338.pdf</t>
+          <t>053_a-classificar_02-10-2023_R$1.610,00_pateo-moinhos-de-vento-adm-e-part-lt.pdf</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -2559,19 +2552,19 @@
       <c r="A55" t="n">
         <v>54</v>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2023-10-17</t>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Claudia</t>
+          <t>Glademir M Machado</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (48 de 143)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2579,8 +2572,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F55" s="2" t="n">
-        <v>4900</v>
+      <c r="F55" s="3" t="n">
+        <v>200</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2589,7 +2582,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(a classificar)\0054_(a classificar)_17-10-2023_R$4.900,00_claudia.pdf</t>
+          <t>054_a-classificar_03-10-2023_R$200,00_glademir-m-machado.pdf</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -2598,19 +2591,19 @@
       <c r="A56" t="n">
         <v>55</v>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2023-10-18</t>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Fernando M Efron</t>
+          <t>Matron Informatica</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>09.279.669/0001-39</t>
+          <t>10.372.701/0001-05 (2 de 2)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2618,8 +2611,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F56" s="2" t="n">
-        <v>550</v>
+      <c r="F56" s="3" t="n">
+        <v>3020</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2628,7 +2621,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(a classificar)\0055_(a classificar)_18-10-2023_R$550,00_fernando_m_efron.pdf</t>
+          <t>055_a-classificar_03-10-2023_R$3.020,00_matron-informatica.pdf</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -2637,58 +2630,54 @@
       <c r="A57" t="n">
         <v>56</v>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2023-10-24</t>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Monica G P Moraes</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>11.400.274/0001-94</t>
-        </is>
-      </c>
+          <t>EDSON DE CAMARGO TRANSPORT (truncado)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F57" s="2" t="n">
-        <v>9427.379999999999</v>
+      <c r="F57" s="3" t="n">
+        <v>700</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>CONCILIADO</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(a classificar)\0056_(a classificar)_24-10-2023_R$9.427,38_monica_g_p_moraes.pdf</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>SEM-COMPROVANTE</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>débito no extrato sem comprovante correspondente</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
         <v>57</v>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2023-10-25</t>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Caleidoskopica Producoes</t>
+          <t>Edson de Camargo Transportes</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (49 de 143)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2696,8 +2685,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F58" s="2" t="n">
-        <v>450</v>
+      <c r="F58" s="3" t="n">
+        <v>700</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2706,7 +2695,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(a classificar)\0057_(a classificar)_25-10-2023_R$450,00_caleidoskopica_producoes.pdf</t>
+          <t>057_a-classificar_05-10-2023_R$700,00_edson-de-camargo-transportes.pdf</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -2715,19 +2704,19 @@
       <c r="A59" t="n">
         <v>58</v>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2023-10-25</t>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>:</t>
+          <t>Amir Labaki</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>46.009.874/0001-00</t>
+          <t>11.400.274/0001-94 (50 de 143)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2735,8 +2724,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F59" s="2" t="n">
-        <v>600</v>
+      <c r="F59" s="3" t="n">
+        <v>500</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2745,7 +2734,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(a classificar)\0058_(a classificar)_25-10-2023_R$600,00_sem_favorecido.pdf</t>
+          <t>058_a-classificar_05-10-2023_R$500,00_amir-labaki.pdf</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -2754,19 +2743,19 @@
       <c r="A60" t="n">
         <v>59</v>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2023-10-25</t>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sofia V Baccarini</t>
+          <t>Memoria Coletiva Imagens e Textos Lt</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (51 de 143)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2774,8 +2763,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F60" s="2" t="n">
-        <v>816.42</v>
+      <c r="F60" s="3" t="n">
+        <v>10500</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2784,7 +2773,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(a classificar)\0059_(a classificar)_25-10-2023_R$816,42_sofia_v_baccarini.pdf</t>
+          <t>059_a-classificar_06-10-2023_R$10.500,00_memoria-coletiva-imagens-e-textos-lt.pdf</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -2793,19 +2782,19 @@
       <c r="A61" t="n">
         <v>60</v>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2023-10-25</t>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-09</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Thiago Augusto Gomas Cunha 397893948</t>
+          <t>Amir Labaki</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (52 de 143)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2813,8 +2802,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F61" s="2" t="n">
-        <v>1800</v>
+      <c r="F61" s="3" t="n">
+        <v>945.49</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2823,7 +2812,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(a classificar)\0060_(a classificar)_25-10-2023_R$1.800,00_thiago_augusto_gomas_cunha_397893948.pdf</t>
+          <t>060_a-classificar_09-10-2023_R$945,49_amir-labaki.pdf</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -2832,19 +2821,19 @@
       <c r="A62" t="n">
         <v>61</v>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2023-10-25</t>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-09</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Maga Projetos Culturais</t>
+          <t>Amir Labaki</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (53 de 143)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2852,38 +2841,42 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F62" s="2" t="n">
-        <v>2000</v>
+      <c r="F62" s="3" t="n">
+        <v>945.49</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>CONCILIADO</t>
+          <t>AMBIGUO</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(a classificar)\0061_(a classificar)_25-10-2023_R$2.000,00_maga_projetos_culturais.pdf</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>061_a-classificar_09-10-2023_R$945,49_amir-labaki.pdf</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>mesmo valor e data de outro comprovante que casou com débito único no extrato — verificar se é pagamento duplicado ou débito não lançado</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
         <v>62</v>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2023-10-25</t>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-09</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Anne Santos</t>
+          <t>Mog Produtora</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (54 de 143)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2891,8 +2884,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F63" s="2" t="n">
-        <v>3600</v>
+      <c r="F63" s="3" t="n">
+        <v>13500</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2901,7 +2894,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(a classificar)\0062_(a classificar)_25-10-2023_R$3.600,00_anne_santos.pdf</t>
+          <t>062_a-classificar_09-10-2023_R$13.500,00_mog-produtora.pdf</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -2910,19 +2903,19 @@
       <c r="A64" t="n">
         <v>63</v>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2023-10-25</t>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-09</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Filmes de Taipa Prod</t>
+          <t>Luis Felipe Monte Cipullo 4425612981</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>28.105.588/0001-67</t>
+          <t>22.592.616/0001-31 (1 de 2)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2930,8 +2923,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F64" s="2" t="n">
-        <v>4500</v>
+      <c r="F64" s="3" t="n">
+        <v>7500</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2940,7 +2933,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(a classificar)\0063_(a classificar)_25-10-2023_R$4.500,00_filmes_de_taipa_prod.pdf</t>
+          <t>063_a-classificar_09-10-2023_R$7.500,00_luis-felipe-monte-cipullo-4425612981.pdf</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -2949,9 +2942,9 @@
       <c r="A65" t="n">
         <v>64</v>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2023-10-25</t>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-09</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2961,7 +2954,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (55 de 143)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2969,7 +2962,7 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F65" s="2" t="n">
+      <c r="F65" s="3" t="n">
         <v>4800</v>
       </c>
       <c r="G65" t="inlineStr">
@@ -2979,7 +2972,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(a classificar)\0064_(a classificar)_25-10-2023_R$4.800,00_thiago_augusto_gomas_cunha_397893948.pdf</t>
+          <t>064_a-classificar_09-10-2023_R$4.800,00_thiago-augusto-gomas-cunha-397893948.pdf</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -2988,19 +2981,19 @@
       <c r="A66" t="n">
         <v>65</v>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2023-10-25</t>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-09</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Mog Produtora</t>
+          <t>Fabio Baltar Duarte</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (56 de 143)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3008,8 +3001,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F66" s="2" t="n">
-        <v>13500</v>
+      <c r="F66" s="3" t="n">
+        <v>1800</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3018,7 +3011,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(a classificar)\0065_(a classificar)_25-10-2023_R$13.500,00_mog_produtora.pdf</t>
+          <t>065_a-classificar_09-10-2023_R$1.800,00_fabio-baltar-duarte.pdf</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -3027,19 +3020,19 @@
       <c r="A67" t="n">
         <v>66</v>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2023-10-25</t>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-09</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Fogo Filmes Ltda</t>
+          <t>Fabio Baltar Duarte</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (57 de 143)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3047,8 +3040,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F67" s="2" t="n">
-        <v>20625</v>
+      <c r="F67" s="3" t="n">
+        <v>1800.01</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3057,7 +3050,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(a classificar)\0066_(a classificar)_25-10-2023_R$20.625,00_fogo_filmes_ltda.pdf</t>
+          <t>066_a-classificar_09-10-2023_R$1.800,01_fabio-baltar-duarte.pdf</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -3066,19 +3059,19 @@
       <c r="A68" t="n">
         <v>67</v>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2023-10-26</t>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-09</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Loc All de Cinema e Televisao Limita</t>
+          <t>Mandala Tours</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>53.563.292.0006-41</t>
+          <t>11.400.274/0001-94 (58 de 143)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3086,8 +3079,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F68" s="2" t="n">
-        <v>995</v>
+      <c r="F68" s="3" t="n">
+        <v>9502.77</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3096,7 +3089,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(a classificar)\0067_(a classificar)_26-10-2023_R$995,00_loc_all_de_cinema_e_televisao_limita.pdf</t>
+          <t>067_a-classificar_09-10-2023_R$9.502,77_mandala-tours.pdf</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -3105,24 +3098,28 @@
       <c r="A69" t="n">
         <v>68</v>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2023-10-26</t>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-09</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>GRIFE RIO LOCADORA LTDA</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>Luis F Monte Cipullo</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>11.400.274/0001-94 (59 de 143)</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F69" s="2" t="n">
-        <v>6550</v>
+      <c r="F69" s="3" t="n">
+        <v>240</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3131,7 +3128,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(a classificar)\0068_(a classificar)_26-10-2023_R$6.550,00_grife_rio_locadora_ltda.pdf</t>
+          <t>068_a-classificar_09-10-2023_R$240,00_luis-f-monte-cipullo.pdf</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -3140,19 +3137,19 @@
       <c r="A70" t="n">
         <v>69</v>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2023-10-26</t>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-09</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Luis Felipe Monte Cipullo 4425612981</t>
+          <t>Andre Lima Monfrini</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>22.592.616/0001-31</t>
+          <t>11.400.274/0001-94 (60 de 143)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3160,8 +3157,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F70" s="2" t="n">
-        <v>7500</v>
+      <c r="F70" s="3" t="n">
+        <v>240</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3170,7 +3167,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(a classificar)\0069_(a classificar)_26-10-2023_R$7.500,00_luis_felipe_monte_cipullo_4425612981.pdf</t>
+          <t>069_a-classificar_09-10-2023_R$240,00_andre-lima-monfrini.pdf</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -3179,19 +3176,19 @@
       <c r="A71" t="n">
         <v>70</v>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2023-10-26</t>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-09</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Filmes de Taipa Prod</t>
+          <t>Felipe G Rosa</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (61 de 143)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3199,8 +3196,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F71" s="2" t="n">
-        <v>11250</v>
+      <c r="F71" s="3" t="n">
+        <v>240</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3209,7 +3206,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(a classificar)\0070_(a classificar)_26-10-2023_R$11.250,00_filmes_de_taipa_prod.pdf</t>
+          <t>070_a-classificar_09-10-2023_R$240,00_felipe-g-rosa.pdf</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -3218,19 +3215,19 @@
       <c r="A72" t="n">
         <v>71</v>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>2023-10-30</t>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-09</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Arthur Rodrigues - Locação de equipamento</t>
+          <t>Thiago A Gomas Cunha</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>33.242.286/0001-70</t>
+          <t>11.400.274/0001-94 (62 de 143)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3238,8 +3235,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F72" s="2" t="n">
-        <v>450</v>
+      <c r="F72" s="3" t="n">
+        <v>240</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3248,7 +3245,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(a classificar)\0071_(a classificar)_30-10-2023_R$450,00_arthur_rodrigues_locacao_de_equipamento.pdf</t>
+          <t>071_a-classificar_09-10-2023_R$240,00_thiago-a-gomas-cunha.pdf</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -3257,58 +3254,54 @@
       <c r="A73" t="n">
         <v>72</v>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2023-10-30</t>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Martina Milla Raffaelli Me</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>11.400.274/0001-94</t>
-        </is>
-      </c>
+          <t>Andre Lima Monfrini (truncado)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F73" s="2" t="n">
-        <v>1500</v>
+      <c r="F73" s="3" t="n">
+        <v>500</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>CONCILIADO</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>(a classificar)\0072_(a classificar)_30-10-2023_R$1.500,00_martina_milla_raffaelli_me.pdf</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>SEM-COMPROVANTE</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>débito no extrato sem comprovante correspondente</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
         <v>73</v>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>2023-10-30</t>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Windsor Administracao de Hoteis e Se</t>
+          <t>Faculdade de Arquitetura e Urbanismo</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (63 de 143)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3316,8 +3309,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F74" s="2" t="n">
-        <v>1559.33</v>
+      <c r="F74" s="3" t="n">
+        <v>2300</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3326,7 +3319,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(a classificar)\0073_(a classificar)_30-10-2023_R$1.559,33_windsor_administracao_de_hoteis_e_se.pdf</t>
+          <t>073_a-classificar_10-10-2023_R$2.300,00_faculdade-de-arquitetura-e-urbanismo.pdf</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -3335,19 +3328,19 @@
       <c r="A75" t="n">
         <v>74</v>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>2023-10-30</t>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Windsor Administracao de Hoteis e Se</t>
+          <t>Ana Beatriz Hermanson Pomar Servicos</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (64 de 143)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3355,8 +3348,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F75" s="2" t="n">
-        <v>2529.85</v>
+      <c r="F75" s="3" t="n">
+        <v>1500</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3365,7 +3358,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(a classificar)\0074_(a classificar)_30-10-2023_R$2.529,85_windsor_administracao_de_hoteis_e_se.pdf</t>
+          <t>074_a-classificar_11-10-2023_R$1.500,00_ana-beatriz-hermanson-pomar-servicos.pdf</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -3374,19 +3367,19 @@
       <c r="A76" t="n">
         <v>75</v>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>2023-10-31</t>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Andre Lima Manfrim</t>
+          <t>Aamac</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (65 de 143)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3394,8 +3387,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F76" s="2" t="n">
-        <v>200</v>
+      <c r="F76" s="3" t="n">
+        <v>400</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3404,7 +3397,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(a classificar)\0075_(a classificar)_31-10-2023_R$200,00_andre_lima_manfrim.pdf</t>
+          <t>075_a-classificar_11-10-2023_R$400,00_aamac.pdf</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -3413,19 +3406,19 @@
       <c r="A77" t="n">
         <v>76</v>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>2023-10-31</t>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Jefferson S Oliveira</t>
+          <t>Malnes Transporte e Produção</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (66 de 143)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3433,8 +3426,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F77" s="2" t="n">
-        <v>320</v>
+      <c r="F77" s="3" t="n">
+        <v>500</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3443,7 +3436,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(a classificar)\0076_(a classificar)_31-10-2023_R$320,00_jefferson_s_oliveira.pdf</t>
+          <t>076_a-classificar_11-10-2023_R$500,00_malnes-transporte-e-producao.pdf</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -3452,19 +3445,19 @@
       <c r="A78" t="n">
         <v>77</v>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>2023-11-01</t>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Windsor Administracao de Hoteis e Se</t>
+          <t>Vondoc Filmes Ltda</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (67 de 143)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3472,8 +3465,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F78" s="2" t="n">
-        <v>316.23</v>
+      <c r="F78" s="3" t="n">
+        <v>4000</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3482,7 +3475,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(a classificar)\0077_(a classificar)_01-11-2023_R$316,23_windsor_administracao_de_hoteis_e_se.pdf</t>
+          <t>077_a-classificar_11-10-2023_R$4.000,00_vondoc-filmes-ltda.pdf</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -3491,19 +3484,19 @@
       <c r="A79" t="n">
         <v>78</v>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>2023-11-08</t>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cristhiano Rodrigues de Jesus 041338</t>
+          <t>Idalina S R Silva</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (68 de 143)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3511,8 +3504,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F79" s="2" t="n">
-        <v>4750</v>
+      <c r="F79" s="3" t="n">
+        <v>1000</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3521,7 +3514,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(a classificar)\0078_(a classificar)_08-11-2023_R$4.750,00_cristhiano_rodrigues_de_jesus_041338.pdf</t>
+          <t>078_a-classificar_11-10-2023_R$1.000,00_idalina-s-r-silva.pdf</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -3530,19 +3523,19 @@
       <c r="A80" t="n">
         <v>79</v>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>2023-11-14</t>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Filmes de Taipa Prod</t>
+          <t>Mandala Tours</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>28.105.588/0001-67</t>
+          <t>11.400.274/0001-94 (69 de 143)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3550,8 +3543,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F80" s="2" t="n">
-        <v>400</v>
+      <c r="F80" s="3" t="n">
+        <v>9672</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3560,7 +3553,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(a classificar)\0079_(a classificar)_14-11-2023_R$400,00_filmes_de_taipa_prod.pdf</t>
+          <t>079_a-classificar_11-10-2023_R$9.672,00_mandala-tours.pdf</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -3569,19 +3562,19 @@
       <c r="A81" t="n">
         <v>80</v>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>2023-11-14</t>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bie Cinema e Tv Ltda Me</t>
+          <t>Andre Lima Monfrini</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>59.875.666/0001-36</t>
+          <t>11.400.274/0001-94 (70 de 143)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3589,8 +3582,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F81" s="2" t="n">
-        <v>750</v>
+      <c r="F81" s="3" t="n">
+        <v>1200</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3599,7 +3592,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(a classificar)\0080_(a classificar)_14-11-2023_R$750,00_bie_cinema_e_tv_ltda_me.pdf</t>
+          <t>080_a-classificar_13-10-2023_R$1.200,00_andre-lima-monfrini.pdf</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -3608,19 +3601,19 @@
       <c r="A82" t="n">
         <v>81</v>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>2023-11-14</t>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Mog Produtora</t>
+          <t>Felipe G Rosa</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (71 de 143)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3628,8 +3621,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F82" s="2" t="n">
-        <v>27000</v>
+      <c r="F82" s="3" t="n">
+        <v>1200</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3638,7 +3631,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(a classificar)\0081_(a classificar)_14-11-2023_R$27.000,00_mog_produtora.pdf</t>
+          <t>081_a-classificar_13-10-2023_R$1.200,00_felipe-g-rosa.pdf</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -3647,19 +3640,19 @@
       <c r="A83" t="n">
         <v>82</v>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>2023-11-27</t>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Fogo Filmes Ltda</t>
+          <t>Luis F Monte Cipullo</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (72 de 143)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3667,8 +3660,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F83" s="2" t="n">
-        <v>20625</v>
+      <c r="F83" s="3" t="n">
+        <v>1200</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3677,7 +3670,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(a classificar)\0082_(a classificar)_27-11-2023_R$20.625,00_fogo_filmes_ltda.pdf</t>
+          <t>082_a-classificar_13-10-2023_R$1.200,00_luis-f-monte-cipullo.pdf</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -3686,19 +3679,19 @@
       <c r="A84" t="n">
         <v>83</v>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>2023-12-11</t>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Memoria Coletiva Imagens e Textos Lt</t>
+          <t>Thiago A Gomas Cunha</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (73 de 143)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3706,8 +3699,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F84" s="2" t="n">
-        <v>2000</v>
+      <c r="F84" s="3" t="n">
+        <v>1200</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3716,7 +3709,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(a classificar)\0083_(a classificar)_11-12-2023_R$2.000,00_memoria_coletiva_imagens_e_textos_lt.pdf</t>
+          <t>083_a-classificar_13-10-2023_R$1.200,00_thiago-a-gomas-cunha.pdf</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -3725,19 +3718,19 @@
       <c r="A85" t="n">
         <v>84</v>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>2023-12-20</t>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Raquel de Oliveira Lazaro 0483723061</t>
+          <t>Andre Lima Manfrim</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (74 de 143)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3745,8 +3738,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F85" s="2" t="n">
-        <v>585</v>
+      <c r="F85" s="3" t="n">
+        <v>1000</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3755,7 +3748,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(a classificar)\0084_(a classificar)_20-12-2023_R$585,00_raquel_de_oliveira_lazaro_0483723061.pdf</t>
+          <t>084_a-classificar_13-10-2023_R$1.000,00_andre-lima-manfrim.pdf</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -3764,19 +3757,19 @@
       <c r="A86" t="n">
         <v>85</v>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>2023-12-20</t>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Fogo Filmes Ltda</t>
+          <t>Idalina S R Silva</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (75 de 143)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3784,8 +3777,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F86" s="2" t="n">
-        <v>20625</v>
+      <c r="F86" s="3" t="n">
+        <v>480</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3794,7 +3787,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(a classificar)\0085_(a classificar)_20-12-2023_R$20.625,00_fogo_filmes_ltda.pdf</t>
+          <t>085_a-classificar_13-10-2023_R$480,00_idalina-s-r-silva.pdf</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -3803,19 +3796,19 @@
       <c r="A87" t="n">
         <v>86</v>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>2024-01-24</t>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Fogo Filmes Ltda</t>
+          <t>Anne C Melo Santos</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (76 de 143)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3823,8 +3816,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F87" s="2" t="n">
-        <v>20625</v>
+      <c r="F87" s="3" t="n">
+        <v>480</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3833,7 +3826,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(a classificar)\0086_(a classificar)_24-01-2024_R$20.625,00_fogo_filmes_ltda.pdf</t>
+          <t>086_a-classificar_13-10-2023_R$480,00_anne-c-melo-santos.pdf</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -3842,19 +3835,19 @@
       <c r="A88" t="n">
         <v>87</v>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>2024-01-31</t>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>In Sampa Courier Entregas Eireli</t>
+          <t>Ricardo Dias Santos</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (77 de 143)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3862,8 +3855,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F88" s="2" t="n">
-        <v>487.2</v>
+      <c r="F88" s="3" t="n">
+        <v>300</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3872,7 +3865,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(a classificar)\0087_(a classificar)_31-01-2024_R$487,20_in_sampa_courier_entregas_eireli.pdf</t>
+          <t>087_a-classificar_13-10-2023_R$300,00_ricardo-dias-santos.pdf</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -3881,19 +3874,19 @@
       <c r="A89" t="n">
         <v>88</v>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>2024-02-23</t>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Juba Producoes</t>
+          <t>Maga Projetos Culturais</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (78 de 143)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3901,8 +3894,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F89" s="2" t="n">
-        <v>6000</v>
+      <c r="F89" s="3" t="n">
+        <v>2000</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -3911,7 +3904,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(a classificar)\0088_(a classificar)_23-02-2024_R$6.000,00_juba_producoes.pdf</t>
+          <t>088_a-classificar_13-10-2023_R$2.000,00_maga-projetos-culturais.pdf</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -3920,19 +3913,19 @@
       <c r="A90" t="n">
         <v>89</v>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>2024-02-23</t>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Fogo Filmes</t>
+          <t>Camila Licariao de Carvalho Braune 4</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>36.584.511/0001- (1 de 2)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3940,8 +3933,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F90" s="2" t="n">
-        <v>22500</v>
+      <c r="F90" s="3" t="n">
+        <v>3000</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3950,7 +3943,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(a classificar)\0089_(a classificar)_23-02-2024_R$22.500,00_fogo_filmes.pdf</t>
+          <t>089_a-classificar_16-10-2023_R$3.000,00_camila-licariao-de-carvalho-braune-4.pdf</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -3959,19 +3952,19 @@
       <c r="A91" t="n">
         <v>90</v>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>2024-05-07</t>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Julia Barbara Melo de Sousa 40926175</t>
+          <t>Camila Licariao de Carvalho Braune 4</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>36.584.511/0001- (2 de 2)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3979,38 +3972,42 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F91" s="2" t="n">
-        <v>4000</v>
+      <c r="F91" s="3" t="n">
+        <v>3000</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>CONCILIADO</t>
+          <t>AMBIGUO</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(a classificar)\0090_(a classificar)_07-05-2024_R$4.000,00_julia_barbara_melo_de_sousa_40926175.pdf</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>090_a-classificar_16-10-2023_R$3.000,00_camila-licariao-de-carvalho-braune-4.pdf</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>mesmo valor e data de outro comprovante que casou com débito único no extrato — verificar se é pagamento duplicado ou débito não lançado</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
         <v>91</v>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>2024-05-31</t>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ganzah</t>
+          <t>Luz Rio Locacao de Equipamentos Cine</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (79 de 143)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4018,8 +4015,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F92" s="2" t="n">
-        <v>5000</v>
+      <c r="F92" s="3" t="n">
+        <v>1100</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -4028,7 +4025,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(a classificar)\0091_(a classificar)_31-05-2024_R$5.000,00_ganzah.pdf</t>
+          <t>091_a-classificar_16-10-2023_R$1.100,00_luz-rio-locacao-de-equipamentos-cine.pdf</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -4037,19 +4034,19 @@
       <c r="A93" t="n">
         <v>92</v>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>2024-06-03</t>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Fogo Filmes</t>
+          <t>Cristhiano Rodrigues de Jesus 041338</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (80 de 143)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4057,8 +4054,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F93" s="2" t="n">
-        <v>13500</v>
+      <c r="F93" s="3" t="n">
+        <v>4375</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -4067,7 +4064,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(a classificar)\0092_(a classificar)_03-06-2024_R$13.500,00_fogo_filmes.pdf</t>
+          <t>092_a-classificar_17-10-2023_R$4.375,00_cristhiano-rodrigues-de-jesus-041338.pdf</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -4076,19 +4073,19 @@
       <c r="A94" t="n">
         <v>93</v>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>2024-07-03</t>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Giovana Amano</t>
+          <t>Claudia</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (81 de 143)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4096,8 +4093,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F94" s="2" t="n">
-        <v>5000</v>
+      <c r="F94" s="3" t="n">
+        <v>4900</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -4106,7 +4103,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(a classificar)\0093_(a classificar)_03-07-2024_R$5.000,00_giovana_amano.pdf</t>
+          <t>093_a-classificar_17-10-2023_R$4.900,00_claudia.pdf</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -4115,19 +4112,19 @@
       <c r="A95" t="n">
         <v>94</v>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>2024-07-30</t>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brasil Imagem</t>
+          <t>Fernando M Efron</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>18.148.355/0001-98</t>
+          <t>09.279.669/0001-39</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4135,8 +4132,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F95" s="2" t="n">
-        <v>8000</v>
+      <c r="F95" s="3" t="n">
+        <v>550</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -4145,7 +4142,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(a classificar)\0094_(a classificar)_30-07-2024_R$8.000,00_brasil_imagem.pdf</t>
+          <t>094_a-classificar_18-10-2023_R$550,00_fernando-m-efron.pdf</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -4154,19 +4151,19 @@
       <c r="A96" t="n">
         <v>95</v>
       </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>2024-08-09</t>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Biblioteca Nacional - Licenciamento</t>
+          <t>Monica G P Moraes</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>11400274/0001-94</t>
+          <t>11.400.274/0001-94 (82 de 143)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4174,8 +4171,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F96" s="2" t="n">
-        <v>550</v>
+      <c r="F96" s="3" t="n">
+        <v>9427.379999999999</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -4184,7 +4181,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(a classificar)\0095_(a classificar)_09-08-2024_R$550,00_biblioteca_nacional_licenciamento.pdf</t>
+          <t>095_a-classificar_24-10-2023_R$9.427,38_monica-g-p-moraes.pdf</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -4193,24 +4190,28 @@
       <c r="A97" t="n">
         <v>96</v>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>2024-08-09</t>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ANJO AZUL FILMES LTDA.</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
+          <t>Mog Produtora</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>11.400.274/0001-94 (83 de 143)</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F97" s="2" t="n">
-        <v>2815</v>
+      <c r="F97" s="3" t="n">
+        <v>10000</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -4219,7 +4220,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(a classificar)\0096_(a classificar)_09-08-2024_R$2.815,00_anjo_azul_filmes_ltda.pdf</t>
+          <t>096_a-classificar_25-10-2023_R$10.000,00_mog-produtora.pdf</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -4228,19 +4229,19 @@
       <c r="A98" t="n">
         <v>97</v>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>2024-08-09</t>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sociedade Amigos da Cinemateca - Sac</t>
+          <t>Fogo Filmes Ltda</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (84 de 143)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4248,8 +4249,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F98" s="2" t="n">
-        <v>2873</v>
+      <c r="F98" s="3" t="n">
+        <v>20625</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -4258,7 +4259,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(a classificar)\0097_(a classificar)_09-08-2024_R$2.873,00_sociedade_amigos_da_cinemateca_sac.pdf</t>
+          <t>097_a-classificar_25-10-2023_R$20.625,00_fogo-filmes-ltda.pdf</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -4267,19 +4268,19 @@
       <c r="A99" t="n">
         <v>98</v>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>2024-08-09</t>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>F. Werneck Barcinski Ltda</t>
+          <t>Anne Santos</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (85 de 143)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4287,8 +4288,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F99" s="2" t="n">
-        <v>4000</v>
+      <c r="F99" s="3" t="n">
+        <v>3600</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -4297,7 +4298,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(a classificar)\0098_(a classificar)_09-08-2024_R$4.000,00_f_werneck_barcinski_ltda.pdf</t>
+          <t>098_a-classificar_25-10-2023_R$3.600,00_anne-santos.pdf</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -4306,19 +4307,19 @@
       <c r="A100" t="n">
         <v>99</v>
       </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>2024-08-16</t>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>:</t>
+          <t>Mog Produtora</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>33.641.663/0001-44</t>
+          <t>11.400.274/0001-94 (86 de 143)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4326,8 +4327,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F100" s="2" t="n">
-        <v>130</v>
+      <c r="F100" s="3" t="n">
+        <v>13500</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -4336,7 +4337,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(a classificar)\0099_(a classificar)_16-08-2024_R$130,00_sem_favorecido.pdf</t>
+          <t>099_a-classificar_25-10-2023_R$13.500,00_mog-produtora.pdf</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -4345,19 +4346,19 @@
       <c r="A101" t="n">
         <v>100</v>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>2024-08-19</t>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Sociedade Amigos da Cinemateca - Sac</t>
+          <t>Mog Produtora</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (87 de 143)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -4365,38 +4366,42 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F101" s="2" t="n">
-        <v>8627</v>
+      <c r="F101" s="3" t="n">
+        <v>10000</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>CONCILIADO</t>
+          <t>AMBIGUO</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(a classificar)\0100_(a classificar)_19-08-2024_R$8.627,00_sociedade_amigos_da_cinemateca_sac.pdf</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>100_a-classificar_25-10-2023_R$10.000,00_mog-produtora.pdf</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>mesmo valor e data de outro comprovante que casou com débito único no extrato — verificar se é pagamento duplicado ou débito não lançado</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
         <v>101</v>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>2024-09-03</t>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Camila Braune</t>
+          <t>Maga Projetos Culturais</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (88 de 143)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4404,8 +4409,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F102" s="2" t="n">
-        <v>600</v>
+      <c r="F102" s="3" t="n">
+        <v>2000</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -4414,7 +4419,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(a classificar)\0101_(a classificar)_03-09-2024_R$600,00_camila_braune.pdf</t>
+          <t>101_a-classificar_25-10-2023_R$2.000,00_maga-projetos-culturais.pdf</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -4423,19 +4428,19 @@
       <c r="A103" t="n">
         <v>102</v>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>2024-09-05</t>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>GLOBO COMUNICACAO E PARTICIPACOES S.A. - CNPJ: 27.865.757/0001-02</t>
+          <t>Thiago Augusto Gomas Cunha 397893948</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>27.865.757/0001-02</t>
+          <t>11.400.274/0001-94 (89 de 143)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4443,8 +4448,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F103" s="2" t="n">
-        <v>938.5</v>
+      <c r="F103" s="3" t="n">
+        <v>1800</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -4453,7 +4458,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(a classificar)\0102_(a classificar)_05-09-2024_R$938,50_globo_comunicacao_e_participacoes_s_a_cnpj_27_865_757_0001_02.pdf</t>
+          <t>102_a-classificar_25-10-2023_R$1.800,00_thiago-augusto-gomas-cunha-397893948.pdf</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -4462,24 +4467,28 @@
       <c r="A104" t="n">
         <v>103</v>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>2024-09-17</t>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>LAPFILME P C LTDA</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
+          <t>Thiago Augusto Gomas Cunha 397893948</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>11.400.274/0001-94 (90 de 143)</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F104" s="2" t="n">
-        <v>2250</v>
+      <c r="F104" s="3" t="n">
+        <v>4800</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -4488,7 +4497,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(a classificar)\0103_(a classificar)_17-09-2024_R$2.250,00_lapfilme_p_c_ltda.pdf</t>
+          <t>103_a-classificar_25-10-2023_R$4.800,00_thiago-augusto-gomas-cunha-397893948.pdf</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -4497,19 +4506,19 @@
       <c r="A105" t="n">
         <v>104</v>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>2024-09-17</t>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>S.A. O ESTADO DE S.PAULO CNPJ 61.533.949/0001-41</t>
+          <t>Sofia V Baccarini</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>011.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (91 de 143)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4517,8 +4526,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F105" s="2" t="n">
-        <v>2632.45</v>
+      <c r="F105" s="3" t="n">
+        <v>816.42</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -4527,7 +4536,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(a classificar)\0104_(a classificar)_17-09-2024_R$2.632,45_s_a_o_estado_de_s_paulo_cnpj_61_533_949_0001_41.pdf</t>
+          <t>104_a-classificar_25-10-2023_R$816,42_sofia-v-baccarini.pdf</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -4536,19 +4545,19 @@
       <c r="A106" t="n">
         <v>105</v>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>2024-09-23</t>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>:</t>
+          <t>Caleidoskopica Producoes</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>08.561.701/0001-01</t>
+          <t>11.400.274/0001-94 (92 de 143)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4556,8 +4565,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F106" s="2" t="n">
-        <v>5500</v>
+      <c r="F106" s="3" t="n">
+        <v>450</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -4566,7 +4575,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(a classificar)\0105_(a classificar)_23-09-2024_R$5.500,00_sem_favorecido.pdf</t>
+          <t>105_a-classificar_25-10-2023_R$450,00_caleidoskopica-producoes.pdf</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -4575,19 +4584,19 @@
       <c r="A107" t="n">
         <v>106</v>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>2024-09-25</t>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Cotacao D.t.v.m. S/a - Sefic</t>
+          <t>Filmes de Taipa Prod</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>28.105.588/0001-67 (1 de 2)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4595,8 +4604,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F107" s="2" t="n">
-        <v>6726.23</v>
+      <c r="F107" s="3" t="n">
+        <v>4500</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -4605,7 +4614,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(a classificar)\0106_(a classificar)_25-09-2024_R$6.726,23_cotacao_d_t_v_m_s_a_sefic.pdf</t>
+          <t>106_a-classificar_25-10-2023_R$4.500,00_filmes-de-taipa-prod.pdf</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -4614,19 +4623,19 @@
       <c r="A108" t="n">
         <v>107</v>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2024-09-30</t>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>do Contribuinte</t>
+          <t>:</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>11400274/0001-94</t>
+          <t>46.009.874/0001-00</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4634,8 +4643,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F108" s="2" t="n">
-        <v>700</v>
+      <c r="F108" s="3" t="n">
+        <v>600</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -4644,7 +4653,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(a classificar)\0107_(a classificar)_30-09-2024_R$700,00_do_contribuinte.pdf</t>
+          <t>107_a-classificar_25-10-2023_R$600,00_sem-nome.pdf</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -4653,19 +4662,19 @@
       <c r="A109" t="n">
         <v>108</v>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2024-09-30</t>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>do Contribuinte</t>
+          <t>Filmes de Taipa Prod</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>11400274/0001-94</t>
+          <t>11.400.274/0001-94 (93 de 143)</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -4673,8 +4682,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F109" s="2" t="n">
-        <v>2400</v>
+      <c r="F109" s="3" t="n">
+        <v>11250</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -4683,7 +4692,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(a classificar)\0108_(a classificar)_30-09-2024_R$2.400,00_do_contribuinte.pdf</t>
+          <t>108_a-classificar_26-10-2023_R$11.250,00_filmes-de-taipa-prod.pdf</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -4692,28 +4701,24 @@
       <c r="A110" t="n">
         <v>109</v>
       </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>2024-10-10</t>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Sociedade Amigos da Cinemateca - Sac</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>11.400.274/0001-94</t>
-        </is>
-      </c>
+          <t>GRIFE RIO LOCADORA LTDA</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F110" s="2" t="n">
-        <v>372</v>
+      <c r="F110" s="3" t="n">
+        <v>6550</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -4722,7 +4727,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(a classificar)\0109_(a classificar)_10-10-2024_R$372,00_sociedade_amigos_da_cinemateca_sac.pdf</t>
+          <t>109_a-classificar_26-10-2023_R$6.550,00_grife-rio-locadora-ltda.pdf</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -4731,19 +4736,19 @@
       <c r="A111" t="n">
         <v>110</v>
       </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>2024-10-10</t>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Cotacao D.t.v.m. S/a - Sefic</t>
+          <t>Loc All de Cinema e Televisao Limita</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>53.563.292.0006-41</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4751,8 +4756,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F111" s="2" t="n">
-        <v>1836.22</v>
+      <c r="F111" s="3" t="n">
+        <v>995</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -4761,7 +4766,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(a classificar)\0110_(a classificar)_10-10-2024_R$1.836,22_cotacao_d_t_v_m_s_a_sefic.pdf</t>
+          <t>110_a-classificar_26-10-2023_R$995,00_loc-all-de-cinema-e-televisao-limita.pdf</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -4770,19 +4775,19 @@
       <c r="A112" t="n">
         <v>111</v>
       </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>2024-10-31</t>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Porviroscopio Projetos C. C. Ltda</t>
+          <t>Luis Felipe Monte Cipullo 4425612981</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>22.592.616/0001-31 (2 de 2)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4790,8 +4795,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F112" s="2" t="n">
-        <v>5000</v>
+      <c r="F112" s="3" t="n">
+        <v>7500</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -4800,7 +4805,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(a classificar)\0111_(a classificar)_31-10-2024_R$5.000,00_porviroscopio_projetos_c_c_ltda.pdf</t>
+          <t>111_a-classificar_26-10-2023_R$7.500,00_luis-felipe-monte-cipullo-4425612981.pdf</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -4809,19 +4814,19 @@
       <c r="A113" t="n">
         <v>112</v>
       </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>2024-10-31</t>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Caliban Producoes Cinematograficas L</t>
+          <t>Windsor Administracao de Hoteis e Se</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (94 de 143)</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4829,8 +4834,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F113" s="2" t="n">
-        <v>5500</v>
+      <c r="F113" s="3" t="n">
+        <v>2529.85</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -4839,7 +4844,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(a classificar)\0112_(a classificar)_31-10-2024_R$5.500,00_caliban_producoes_cinematograficas_l.pdf</t>
+          <t>112_a-classificar_30-10-2023_R$2.529,85_windsor-administracao-de-hoteis-e-se.pdf</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -4848,24 +4853,28 @@
       <c r="A114" t="n">
         <v>113</v>
       </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>2024-11-01</t>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>do Contribuinte</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
+          <t>Windsor Administracao de Hoteis e Se</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>11.400.274/0001-94 (95 de 143)</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F114" s="2" t="n">
-        <v>140</v>
+      <c r="F114" s="3" t="n">
+        <v>1559.33</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -4874,7 +4883,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(a classificar)\0113_(a classificar)_01-11-2024_R$140,00_do_contribuinte.pdf</t>
+          <t>113_a-classificar_30-10-2023_R$1.559,33_windsor-administracao-de-hoteis-e-se.pdf</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -4883,19 +4892,19 @@
       <c r="A115" t="n">
         <v>114</v>
       </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>2024-11-04</t>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>do Contribuinte</t>
+          <t>- (truncado)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>11400274/0001-94</t>
+          <t>33.242.286/0001-70</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4903,8 +4912,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F115" s="2" t="n">
-        <v>400</v>
+      <c r="F115" s="3" t="n">
+        <v>450</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -4913,7 +4922,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(a classificar)\0114_(a classificar)_04-11-2024_R$400,00_do_contribuinte.pdf</t>
+          <t>114_a-classificar_30-10-2023_R$450,00_sem-nome.pdf</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -4922,19 +4931,19 @@
       <c r="A116" t="n">
         <v>115</v>
       </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>2024-11-08</t>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Echo S Comunicacao Sonora e Visual</t>
+          <t>Brilho</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (96 de 143)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4942,8 +4951,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F116" s="2" t="n">
-        <v>600</v>
+      <c r="F116" s="3" t="n">
+        <v>211.5</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -4952,28 +4961,32 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(a classificar)\0115_(a classificar)_08-11-2024_R$600,00_echo_s_comunicacao_sonora_e_visual.pdf</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>115_a-classificar_30-10-2023_R$211,50_brilho.pdf</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>valor ilegível no comprovante; assumido do extrato (R$ 211.50)</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
         <v>116</v>
       </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>2024-11-08</t>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Roberto F D Avila</t>
+          <t>Martina Milla Raffaelli Me</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (97 de 143)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4981,8 +4994,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F117" s="2" t="n">
-        <v>1000</v>
+      <c r="F117" s="3" t="n">
+        <v>1500</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -4991,7 +5004,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(a classificar)\0116_(a classificar)_08-11-2024_R$1.000,00_roberto_f_d_avila.pdf</t>
+          <t>116_a-classificar_30-10-2023_R$1.500,00_martina-milla-raffaelli-me.pdf</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -5000,24 +5013,28 @@
       <c r="A118" t="n">
         <v>117</v>
       </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>2024-11-12</t>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>do Contribuinte</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr"/>
+          <t>Jefferson S Oliveira</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>11.400.274/0001-94 (98 de 143)</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F118" s="2" t="n">
-        <v>12</v>
+      <c r="F118" s="3" t="n">
+        <v>320</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -5026,7 +5043,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(a classificar)\0117_(a classificar)_12-11-2024_R$12,00_do_contribuinte.pdf</t>
+          <t>117_a-classificar_31-10-2023_R$320,00_jefferson-s-oliveira.pdf</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -5035,19 +5052,19 @@
       <c r="A119" t="n">
         <v>118</v>
       </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>2024-11-14</t>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>do Contribuinte</t>
+          <t>Felipe G Rosa</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>11400274/0001-94</t>
+          <t>11.400.274/0001-94 (99 de 143)</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -5055,8 +5072,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F119" s="2" t="n">
-        <v>200</v>
+      <c r="F119" s="3" t="n">
+        <v>1020</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -5065,7 +5082,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(a classificar)\0118_(a classificar)_14-11-2024_R$200,00_do_contribuinte.pdf</t>
+          <t>118_a-classificar_31-10-2023_R$1.020,00_felipe-g-rosa.pdf</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -5074,19 +5091,19 @@
       <c r="A120" t="n">
         <v>119</v>
       </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>2024-11-28</t>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Marach Servicos Audiovisuais Eireli</t>
+          <t>Luis F Monte Cipullo</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (100 de 143)</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -5094,8 +5111,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F120" s="2" t="n">
-        <v>230</v>
+      <c r="F120" s="3" t="n">
+        <v>1020</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -5104,7 +5121,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(a classificar)\0119_(a classificar)_28-11-2024_R$230,00_marach_servicos_audiovisuais_eireli.pdf</t>
+          <t>119_a-classificar_31-10-2023_R$1.020,00_luis-f-monte-cipullo.pdf</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -5113,19 +5130,19 @@
       <c r="A121" t="n">
         <v>120</v>
       </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>2024-12-05</t>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Geisa Silva Jesus</t>
+          <t>Andre Lima Monfrini</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (101 de 143)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -5133,8 +5150,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F121" s="2" t="n">
-        <v>1500</v>
+      <c r="F121" s="3" t="n">
+        <v>1020</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -5143,7 +5160,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(a classificar)\0120_(a classificar)_05-12-2024_R$1.500,00_geisa_silva_jesus.pdf</t>
+          <t>120_a-classificar_31-10-2023_R$1.020,00_andre-lima-monfrini.pdf</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -5152,19 +5169,19 @@
       <c r="A122" t="n">
         <v>121</v>
       </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>2024-12-05</t>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>:</t>
+          <t>Andre Lima Manfrim</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>02.903.707/0001-33</t>
+          <t>11.400.274/0001-94 (102 de 143)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -5172,8 +5189,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F122" s="2" t="n">
-        <v>6400</v>
+      <c r="F122" s="3" t="n">
+        <v>200</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -5182,7 +5199,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(a classificar)\0121_(a classificar)_05-12-2024_R$6.400,00_sem_favorecido.pdf</t>
+          <t>121_a-classificar_31-10-2023_R$200,00_andre-lima-manfrim.pdf</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -5191,19 +5208,19 @@
       <c r="A123" t="n">
         <v>122</v>
       </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>2024-12-10</t>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>:</t>
+          <t>Windsor Administracao de Hoteis e Se</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>33.641.663/0001-44</t>
+          <t>11.400.274/0001-94 (103 de 143)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -5211,8 +5228,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F123" s="2" t="n">
-        <v>100</v>
+      <c r="F123" s="3" t="n">
+        <v>316.23</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -5221,7 +5238,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(a classificar)\0122_(a classificar)_10-12-2024_R$100,00_sem_favorecido.pdf</t>
+          <t>122_a-classificar_01-11-2023_R$316,23_windsor-administracao-de-hoteis-e-se.pdf</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -5230,58 +5247,54 @@
       <c r="A124" t="n">
         <v>123</v>
       </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>2024-12-17</t>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Som Livre</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>11.400.274/0001-94</t>
-        </is>
-      </c>
+          <t>BERNARDO TAVARES E SILVA C (truncado)</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F124" s="2" t="n">
-        <v>2000</v>
+      <c r="F124" s="3" t="n">
+        <v>300</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>CONCILIADO</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>(a classificar)\0123_(a classificar)_17-12-2024_R$2.000,00_som_livre.pdf</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>SEM-COMPROVANTE</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>débito no extrato sem comprovante correspondente</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
         <v>124</v>
       </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>2024-12-17</t>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Editora e Importadora Musical Fermat</t>
+          <t>Bernardo T S Costa</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (104 de 143)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -5289,8 +5302,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F125" s="2" t="n">
-        <v>3000</v>
+      <c r="F125" s="3" t="n">
+        <v>300</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -5299,7 +5312,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(a classificar)\0124_(a classificar)_17-12-2024_R$3.000,00_editora_e_importadora_musical_fermat.pdf</t>
+          <t>124_a-classificar_08-11-2023_R$300,00_bernardo-t-s-costa.pdf</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -5308,19 +5321,19 @@
       <c r="A126" t="n">
         <v>125</v>
       </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>2024-12-17</t>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Carlos Lyra Edicoes Musicais</t>
+          <t>Cristhiano Rodrigues de Jesus 041338</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (105 de 143)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -5328,8 +5341,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F126" s="2" t="n">
-        <v>3500</v>
+      <c r="F126" s="3" t="n">
+        <v>4750</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -5338,7 +5351,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(a classificar)\0125_(a classificar)_17-12-2024_R$3.500,00_carlos_lyra_edicoes_musicais.pdf</t>
+          <t>125_a-classificar_08-11-2023_R$4.750,00_cristhiano-rodrigues-de-jesus-041338.pdf</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -5347,19 +5360,19 @@
       <c r="A127" t="n">
         <v>126</v>
       </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>2024-12-17</t>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Cotacao D.t.v.m. S/a - Sefic</t>
+          <t>Mog Produtora</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (106 de 143)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -5367,8 +5380,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F127" s="2" t="n">
-        <v>8393.299999999999</v>
+      <c r="F127" s="3" t="n">
+        <v>27000</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -5377,7 +5390,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(a classificar)\0126_(a classificar)_17-12-2024_R$8.393,30_cotacao_d_t_v_m_s_a_sefic.pdf</t>
+          <t>126_a-classificar_14-11-2023_R$27.000,00_mog-produtora.pdf</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -5386,19 +5399,19 @@
       <c r="A128" t="n">
         <v>127</v>
       </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>2024-12-26</t>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Giovana Amano</t>
+          <t>Monica G P Moraes</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (107 de 143)</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -5406,8 +5419,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F128" s="2" t="n">
-        <v>5000</v>
+      <c r="F128" s="3" t="n">
+        <v>3724.74</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -5416,7 +5429,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(a classificar)\0127_(a classificar)_26-12-2024_R$5.000,00_giovana_amano.pdf</t>
+          <t>127_a-classificar_14-11-2023_R$3.724,74_monica-g-p-moraes.pdf</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -5425,19 +5438,19 @@
       <c r="A129" t="n">
         <v>128</v>
       </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>2025-01-16</t>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Arquivo Nacional - Licenciamento</t>
+          <t>Monica G P Moraes</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>11400274/0001-94</t>
+          <t>11.400.274/0001-94 (108 de 143)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -5445,38 +5458,42 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F129" s="2" t="n">
-        <v>50</v>
+      <c r="F129" s="3" t="n">
+        <v>3724.74</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>CONCILIADO</t>
+          <t>AMBIGUO</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(a classificar)\0128_(a classificar)_16-01-2025_R$50,00_arquivo_nacional_licenciamento.pdf</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
+          <t>128_a-classificar_14-11-2023_R$3.724,74_monica-g-p-moraes.pdf</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>mesmo valor e data de outro comprovante que casou com débito único no extrato — verificar se é pagamento duplicado ou débito não lançado</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
         <v>129</v>
       </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>2025-02-27</t>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Ganzah</t>
+          <t>Bie Cinema e Tv Ltda Me</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>59.875.666/0001-36</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -5484,8 +5501,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F130" s="2" t="n">
-        <v>7000</v>
+      <c r="F130" s="3" t="n">
+        <v>750</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -5494,7 +5511,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(a classificar)\0129_(a classificar)_27-02-2025_R$7.000,00_ganzah.pdf</t>
+          <t>129_a-classificar_14-11-2023_R$750,00_bie-cinema-e-tv-ltda-me.pdf</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -5503,19 +5520,19 @@
       <c r="A131" t="n">
         <v>130</v>
       </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>2025-03-25</t>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>:</t>
+          <t>Filmes de Taipa Prod</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>04.884.574/0001-20</t>
+          <t>28.105.588/0001-67 (2 de 2)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -5523,8 +5540,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F131" s="2" t="n">
-        <v>626.3</v>
+      <c r="F131" s="3" t="n">
+        <v>400</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -5533,7 +5550,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(a classificar)\0130_(a classificar)_25-03-2025_R$626,30_sem_favorecido.pdf</t>
+          <t>130_a-classificar_14-11-2023_R$400,00_filmes-de-taipa-prod.pdf</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -5542,19 +5559,19 @@
       <c r="A132" t="n">
         <v>131</v>
       </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>2025-04-30</t>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Planifilmes Ltda</t>
+          <t>Fogo Filmes Ltda</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (109 de 143)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -5562,8 +5579,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F132" s="2" t="n">
-        <v>1200</v>
+      <c r="F132" s="3" t="n">
+        <v>20625</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -5572,7 +5589,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(a classificar)\0131_(a classificar)_30-04-2025_R$1.200,00_planifilmes_ltda.pdf</t>
+          <t>131_a-classificar_27-11-2023_R$20.625,00_fogo-filmes-ltda.pdf</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -5581,19 +5598,19 @@
       <c r="A133" t="n">
         <v>132</v>
       </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>2025-04-30</t>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>2023-12-11</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Giovana Amano</t>
+          <t>Memoria Coletiva Imagens e Textos Lt</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (110 de 143)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -5601,8 +5618,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F133" s="2" t="n">
-        <v>3000</v>
+      <c r="F133" s="3" t="n">
+        <v>2000</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -5611,7 +5628,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(a classificar)\0132_(a classificar)_30-04-2025_R$3.000,00_giovana_amano.pdf</t>
+          <t>132_a-classificar_11-12-2023_R$2.000,00_memoria-coletiva-imagens-e-textos-lt.pdf</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -5620,19 +5637,19 @@
       <c r="A134" t="n">
         <v>133</v>
       </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>2025-05-07</t>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Fogo Filmes</t>
+          <t>Raquel de Oliveira Lazaro 0483723061</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (111 de 143)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -5640,8 +5657,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F134" s="2" t="n">
-        <v>18093.63</v>
+      <c r="F134" s="3" t="n">
+        <v>585</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -5650,7 +5667,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(a classificar)\0133_(a classificar)_07-05-2025_R$18.093,63_fogo_filmes.pdf</t>
+          <t>133_a-classificar_20-12-2023_R$585,00_raquel-de-oliveira-lazaro-0483723061.pdf</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -5659,19 +5676,19 @@
       <c r="A135" t="n">
         <v>134</v>
       </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>2022-11-10</t>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Luis Felipe Labaki</t>
+          <t>Fogo Filmes Ltda</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (112 de 143)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -5679,8 +5696,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F135" s="2" t="n">
-        <v>1200</v>
+      <c r="F135" s="3" t="n">
+        <v>20625</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -5689,7 +5706,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(a classificar)\0134_(a classificar)_10-11-2022_R$1.200,00_luis_felipe_labaki.pdf</t>
+          <t>134_a-classificar_20-12-2023_R$20.625,00_fogo-filmes-ltda.pdf</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -5698,19 +5715,19 @@
       <c r="A136" t="n">
         <v>135</v>
       </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>2022-11-10</t>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>2024-01-24</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Felipe G Rosa</t>
+          <t>Fogo Filmes Ltda</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (113 de 143)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -5718,8 +5735,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F136" s="2" t="n">
-        <v>1200</v>
+      <c r="F136" s="3" t="n">
+        <v>20625</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -5728,7 +5745,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(a classificar)\0135_(a classificar)_10-11-2022_R$1.200,00_felipe_g_rosa.pdf</t>
+          <t>135_a-classificar_24-01-2024_R$20.625,00_fogo-filmes-ltda.pdf</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -5737,19 +5754,19 @@
       <c r="A137" t="n">
         <v>136</v>
       </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>2023-07-03</t>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Circunstancia Cinematografica e Prod</t>
+          <t>In Sampa Courier Entregas Eireli</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (114 de 143)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -5757,8 +5774,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F137" s="2" t="n">
-        <v>25000</v>
+      <c r="F137" s="3" t="n">
+        <v>487.2</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -5767,7 +5784,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(a classificar)\0136_(a classificar)_03-07-2023_R$25.000,00_circunstancia_cinematografica_e_prod.pdf</t>
+          <t>136_a-classificar_31-01-2024_R$487,20_in-sampa-courier-entregas-eireli.pdf</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -5776,19 +5793,19 @@
       <c r="A138" t="n">
         <v>137</v>
       </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>2023-07-03</t>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Mog Produtora</t>
+          <t>Juba Producoes</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (115 de 143)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -5796,8 +5813,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F138" s="2" t="n">
-        <v>25000</v>
+      <c r="F138" s="3" t="n">
+        <v>6000</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -5806,7 +5823,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(a classificar)\0137_(a classificar)_03-07-2023_R$25.000,00_mog_produtora.pdf</t>
+          <t>137_a-classificar_23-02-2024_R$6.000,00_juba-producoes.pdf</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -5815,19 +5832,19 @@
       <c r="A139" t="n">
         <v>138</v>
       </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>2023-09-20</t>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Gol Linhas Aéreas</t>
+          <t>Fogo Filmes</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (116 de 143)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -5835,8 +5852,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F139" s="2" t="n">
-        <v>1524.64</v>
+      <c r="F139" s="3" t="n">
+        <v>22500</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -5845,7 +5862,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(a classificar)\0138_(a classificar)_20-09-2023_R$1.524,64_gol_linhas_aereas.pdf</t>
+          <t>138_a-classificar_23-02-2024_R$22.500,00_fogo-filmes.pdf</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -5854,19 +5871,19 @@
       <c r="A140" t="n">
         <v>139</v>
       </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>2023-09-20</t>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Gol Linhas Aéreas</t>
+          <t>Julia Barbara Melo de Sousa 40926175</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (117 de 143)</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -5874,8 +5891,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F140" s="2" t="n">
-        <v>1524.64</v>
+      <c r="F140" s="3" t="n">
+        <v>4000</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -5884,7 +5901,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(a classificar)\0139_(a classificar)_20-09-2023_R$1.524,64_gol_linhas_aereas.pdf</t>
+          <t>139_a-classificar_07-05-2024_R$4.000,00_julia-barbara-melo-de-sousa-40926175.pdf</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -5893,19 +5910,19 @@
       <c r="A141" t="n">
         <v>140</v>
       </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>2023-09-20</t>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Gol Linhas Aéreas</t>
+          <t>Ganzah</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (118 de 143)</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -5913,8 +5930,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F141" s="2" t="n">
-        <v>1524.64</v>
+      <c r="F141" s="3" t="n">
+        <v>5000</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -5923,7 +5940,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(a classificar)\0140_(a classificar)_20-09-2023_R$1.524,64_gol_linhas_aereas.pdf</t>
+          <t>140_a-classificar_31-05-2024_R$5.000,00_ganzah.pdf</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -5932,19 +5949,19 @@
       <c r="A142" t="n">
         <v>141</v>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>2023-09-20</t>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Gol Linhas Aéreas</t>
+          <t>Fogo Filmes</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (119 de 143)</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -5952,8 +5969,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F142" s="2" t="n">
-        <v>1524.64</v>
+      <c r="F142" s="3" t="n">
+        <v>13500</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -5962,7 +5979,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(a classificar)\0141_(a classificar)_20-09-2023_R$1.524,64_gol_linhas_aereas.pdf</t>
+          <t>141_a-classificar_03-06-2024_R$13.500,00_fogo-filmes.pdf</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -5971,19 +5988,19 @@
       <c r="A143" t="n">
         <v>142</v>
       </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>2023-09-20</t>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Gol Linhas Aéreas</t>
+          <t>Giovana Amano</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (120 de 143)</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -5991,8 +6008,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F143" s="2" t="n">
-        <v>2870.87</v>
+      <c r="F143" s="3" t="n">
+        <v>5000</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -6001,7 +6018,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(a classificar)\0142_(a classificar)_20-09-2023_R$2.870,87_gol_linhas_aereas.pdf</t>
+          <t>142_a-classificar_03-07-2024_R$5.000,00_giovana-amano.pdf</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -6010,19 +6027,19 @@
       <c r="A144" t="n">
         <v>143</v>
       </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>2023-09-20</t>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Gol Linhas Aéreas</t>
+          <t>Brasil Imagem</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>18.148.355/0001-98</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -6030,8 +6047,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F144" s="2" t="n">
-        <v>2870.87</v>
+      <c r="F144" s="3" t="n">
+        <v>8000</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -6040,7 +6057,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(a classificar)\0143_(a classificar)_20-09-2023_R$2.870,87_gol_linhas_aereas.pdf</t>
+          <t>143_a-classificar_30-07-2024_R$8.000,00_brasil-imagem.pdf</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -6049,28 +6066,24 @@
       <c r="A145" t="n">
         <v>144</v>
       </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>2023-09-20</t>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Gol Linhas Aéreas</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>11.400.274/0001-94</t>
-        </is>
-      </c>
+          <t>ANJO AZUL FILMES LTDA.</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F145" s="2" t="n">
-        <v>2870.87</v>
+      <c r="F145" s="3" t="n">
+        <v>2815</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -6079,7 +6092,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(a classificar)\0144_(a classificar)_20-09-2023_R$2.870,87_gol_linhas_aereas.pdf</t>
+          <t>144_a-classificar_09-08-2024_R$2.815,00_anjo-azul-filmes-ltda.pdf</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -6088,19 +6101,19 @@
       <c r="A146" t="n">
         <v>145</v>
       </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>2023-09-20</t>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Gol Linhas Aéreas</t>
+          <t>Sociedade Amigos da Cinemateca - Sac</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (121 de 143)</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -6108,8 +6121,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F146" s="2" t="n">
-        <v>2870.87</v>
+      <c r="F146" s="3" t="n">
+        <v>2873</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -6118,7 +6131,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(a classificar)\0145_(a classificar)_20-09-2023_R$2.870,87_gol_linhas_aereas.pdf</t>
+          <t>145_a-classificar_09-08-2024_R$2.873,00_sociedade-amigos-da-cinemateca-sac.pdf</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -6127,19 +6140,19 @@
       <c r="A147" t="n">
         <v>146</v>
       </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>2023-09-28</t>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Andre Lima Manfrim</t>
+          <t>F. Werneck Barcinski Ltda</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (122 de 143)</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -6147,8 +6160,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F147" s="2" t="n">
-        <v>1000</v>
+      <c r="F147" s="3" t="n">
+        <v>4000</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -6157,7 +6170,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(a classificar)\0146_(a classificar)_28-09-2023_R$1.000,00_andre_lima_manfrim.pdf</t>
+          <t>146_a-classificar_09-08-2024_R$4.000,00_f-werneck-barcinski-ltda.pdf</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -6166,19 +6179,15 @@
       <c r="A148" t="n">
         <v>147</v>
       </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Sofia V Baccarini</t>
-        </is>
-      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11400274/0001-94 (1 de 6)</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -6186,8 +6195,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F148" s="2" t="n">
-        <v>1000</v>
+      <c r="F148" s="3" t="n">
+        <v>550</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -6196,7 +6205,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(a classificar)\0147_(a classificar)_28-09-2023_R$1.000,00_sofia_v_baccarini.pdf</t>
+          <t>147_a-classificar_09-08-2024_R$550,00_sem-nome.pdf</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -6205,19 +6214,19 @@
       <c r="A149" t="n">
         <v>148</v>
       </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>2023-09-29</t>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Fabio Baltar Duarte</t>
+          <t>:</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>33.641.663/0001-44 (1 de 2)</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -6225,8 +6234,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F149" s="2" t="n">
-        <v>560</v>
+      <c r="F149" s="3" t="n">
+        <v>130</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -6235,7 +6244,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(a classificar)\0148_(a classificar)_29-09-2023_R$560,00_fabio_baltar_duarte.pdf</t>
+          <t>148_a-classificar_16-08-2024_R$130,00_sem-nome.pdf</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -6244,19 +6253,19 @@
       <c r="A150" t="n">
         <v>149</v>
       </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>2023-09-29</t>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Sofia V Baccarini</t>
+          <t>Sociedade Amigos da Cinemateca - Sac</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (123 de 143)</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -6264,8 +6273,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F150" s="2" t="n">
-        <v>560</v>
+      <c r="F150" s="3" t="n">
+        <v>8627</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -6274,7 +6283,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(a classificar)\0149_(a classificar)_29-09-2023_R$560,00_sofia_v_baccarini.pdf</t>
+          <t>149_a-classificar_19-08-2024_R$8.627,00_sociedade-amigos-da-cinemateca-sac.pdf</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -6283,19 +6292,19 @@
       <c r="A151" t="n">
         <v>150</v>
       </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>2023-09-29</t>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Luis F Monte Cipullo</t>
+          <t>Camila Braune</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (124 de 143)</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -6303,8 +6312,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F151" s="2" t="n">
-        <v>1050</v>
+      <c r="F151" s="3" t="n">
+        <v>600</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -6313,7 +6322,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(a classificar)\0150_(a classificar)_29-09-2023_R$1.050,00_luis_f_monte_cipullo.pdf</t>
+          <t>150_a-classificar_03-09-2024_R$600,00_camila-braune.pdf</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -6322,19 +6331,19 @@
       <c r="A152" t="n">
         <v>151</v>
       </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>2023-09-29</t>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Thiago A Gomas Cunha</t>
+          <t>GLOBO COMUNICACAO E PARTICIPACOES S.A. - CNPJ: 27.865.757/0001-02</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>27.865.757/0001-02</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -6342,8 +6351,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F152" s="2" t="n">
-        <v>1050</v>
+      <c r="F152" s="3" t="n">
+        <v>938.5</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -6352,7 +6361,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(a classificar)\0151_(a classificar)_29-09-2023_R$1.050,00_thiago_a_gomas_cunha.pdf</t>
+          <t>151_a-classificar_05-09-2024_R$938,50_globo-comunicacao-e-participacoes-s-a-cnpj-27-865-757-0001-0.pdf</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -6361,28 +6370,24 @@
       <c r="A153" t="n">
         <v>152</v>
       </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>2023-09-29</t>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Andre Lima Monfrini</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>11.400.274/0001-94</t>
-        </is>
-      </c>
+          <t>LAPFILME P C LTDA</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F153" s="2" t="n">
-        <v>1050</v>
+      <c r="F153" s="3" t="n">
+        <v>2250</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -6391,7 +6396,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(a classificar)\0152_(a classificar)_29-09-2023_R$1.050,00_andre_lima_monfrini.pdf</t>
+          <t>152_a-classificar_17-09-2024_R$2.250,00_lapfilme-p-c-ltda.pdf</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -6400,19 +6405,19 @@
       <c r="A154" t="n">
         <v>153</v>
       </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>2023-09-29</t>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Felipe G Rosa</t>
+          <t>S.A. O ESTADO DE S.PAULO CNPJ 61.533.949/0001-41</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>011.400.274/0001-94</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -6420,8 +6425,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F154" s="2" t="n">
-        <v>1050</v>
+      <c r="F154" s="3" t="n">
+        <v>2632.45</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -6430,7 +6435,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(a classificar)\0153_(a classificar)_29-09-2023_R$1.050,00_felipe_g_rosa.pdf</t>
+          <t>153_a-classificar_17-09-2024_R$2.632,45_s-a-o-estado-de-s-paulo-cnpj-61-533-949-0001-41.pdf</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -6439,19 +6444,19 @@
       <c r="A155" t="n">
         <v>154</v>
       </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>2023-10-05</t>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Edson de Camargo Transportes</t>
+          <t>:</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>08.561.701/0001-01</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -6459,8 +6464,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F155" s="2" t="n">
-        <v>700</v>
+      <c r="F155" s="3" t="n">
+        <v>5500</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -6469,7 +6474,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(a classificar)\0154_(a classificar)_05-10-2023_R$700,00_edson_de_camargo_transportes.pdf</t>
+          <t>154_a-classificar_23-09-2024_R$5.500,00_sem-nome.pdf</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -6478,19 +6483,19 @@
       <c r="A156" t="n">
         <v>155</v>
       </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>2023-10-09</t>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Luis F Monte Cipullo</t>
+          <t>Cotacao D.t.v.m. S/a - Sefic</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (125 de 143)</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -6498,8 +6503,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F156" s="2" t="n">
-        <v>240</v>
+      <c r="F156" s="3" t="n">
+        <v>6726.23</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -6508,7 +6513,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(a classificar)\0155_(a classificar)_09-10-2023_R$240,00_luis_f_monte_cipullo.pdf</t>
+          <t>155_a-classificar_25-09-2024_R$6.726,23_cotacao-d-t-v-m-s-a-sefic.pdf</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -6517,19 +6522,19 @@
       <c r="A157" t="n">
         <v>156</v>
       </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>2023-10-09</t>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Thiago A Gomas Cunha</t>
+          <t>do Contribuinte</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11400274/0001-94 (2 de 6)</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -6537,8 +6542,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F157" s="2" t="n">
-        <v>240</v>
+      <c r="F157" s="3" t="n">
+        <v>700</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -6547,7 +6552,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(a classificar)\0156_(a classificar)_09-10-2023_R$240,00_thiago_a_gomas_cunha.pdf</t>
+          <t>156_a-classificar_30-09-2024_R$700,00_do-contribuinte.pdf</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -6556,19 +6561,19 @@
       <c r="A158" t="n">
         <v>157</v>
       </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>2023-10-09</t>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Andre Lima Monfrini</t>
+          <t>do Contribuinte</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11400274/0001-94 (3 de 6)</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -6576,8 +6581,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F158" s="2" t="n">
-        <v>240</v>
+      <c r="F158" s="3" t="n">
+        <v>2400</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -6586,7 +6591,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(a classificar)\0157_(a classificar)_09-10-2023_R$240,00_andre_lima_monfrini.pdf</t>
+          <t>157_a-classificar_30-09-2024_R$2.400,00_do-contribuinte.pdf</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -6595,19 +6600,19 @@
       <c r="A159" t="n">
         <v>158</v>
       </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>2023-10-09</t>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Felipe G Rosa</t>
+          <t>Cotacao D.t.v.m. S/a - Sefic</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (126 de 143)</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -6615,8 +6620,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F159" s="2" t="n">
-        <v>240</v>
+      <c r="F159" s="3" t="n">
+        <v>1836.22</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -6625,7 +6630,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(a classificar)\0158_(a classificar)_09-10-2023_R$240,00_felipe_g_rosa.pdf</t>
+          <t>158_a-classificar_10-10-2024_R$1.836,22_cotacao-d-t-v-m-s-a-sefic.pdf</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -6634,19 +6639,19 @@
       <c r="A160" t="n">
         <v>159</v>
       </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>2023-10-09</t>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Amir Labaki</t>
+          <t>Sociedade Amigos da Cinemateca - Sac</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (127 de 143)</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -6654,8 +6659,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F160" s="2" t="n">
-        <v>945.49</v>
+      <c r="F160" s="3" t="n">
+        <v>372</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -6664,7 +6669,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(a classificar)\0159_(a classificar)_09-10-2023_R$945,49_amir_labaki.pdf</t>
+          <t>159_a-classificar_10-10-2024_R$372,00_sociedade-amigos-da-cinemateca-sac.pdf</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -6673,19 +6678,19 @@
       <c r="A161" t="n">
         <v>160</v>
       </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>2023-10-13</t>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Anne C Melo Santos</t>
+          <t>Porviroscopio Projetos C. C. Ltda</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (128 de 143)</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -6693,8 +6698,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F161" s="2" t="n">
-        <v>480</v>
+      <c r="F161" s="3" t="n">
+        <v>5000</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -6703,7 +6708,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(a classificar)\0160_(a classificar)_13-10-2023_R$480,00_anne_c_melo_santos.pdf</t>
+          <t>160_a-classificar_31-10-2024_R$5.000,00_porviroscopio-projetos-c-c-ltda.pdf</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -6712,19 +6717,19 @@
       <c r="A162" t="n">
         <v>161</v>
       </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>2023-10-13</t>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Idalina S R Silva</t>
+          <t>Caliban Producoes Cinematograficas L</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (129 de 143)</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -6732,8 +6737,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F162" s="2" t="n">
-        <v>480</v>
+      <c r="F162" s="3" t="n">
+        <v>5500</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -6742,7 +6747,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(a classificar)\0161_(a classificar)_13-10-2023_R$480,00_idalina_s_r_silva.pdf</t>
+          <t>161_a-classificar_31-10-2024_R$5.500,00_caliban-producoes-cinematograficas-l.pdf</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -6751,28 +6756,24 @@
       <c r="A163" t="n">
         <v>162</v>
       </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>2023-10-13</t>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Luis F Monte Cipullo</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>11.400.274/0001-94</t>
-        </is>
-      </c>
+          <t>do Contribuinte</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F163" s="2" t="n">
-        <v>1200</v>
+      <c r="F163" s="3" t="n">
+        <v>140</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -6781,7 +6782,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(a classificar)\0162_(a classificar)_13-10-2023_R$1.200,00_luis_f_monte_cipullo.pdf</t>
+          <t>162_a-classificar_01-11-2024_R$140,00_do-contribuinte.pdf</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -6790,19 +6791,19 @@
       <c r="A164" t="n">
         <v>163</v>
       </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>2023-10-13</t>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Thiago A Gomas Cunha</t>
+          <t>do Contribuinte</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11400274/0001-94 (4 de 6)</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -6810,8 +6811,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F164" s="2" t="n">
-        <v>1200</v>
+      <c r="F164" s="3" t="n">
+        <v>400</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -6820,7 +6821,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(a classificar)\0163_(a classificar)_13-10-2023_R$1.200,00_thiago_a_gomas_cunha.pdf</t>
+          <t>163_a-classificar_04-11-2024_R$400,00_do-contribuinte.pdf</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -6829,19 +6830,19 @@
       <c r="A165" t="n">
         <v>164</v>
       </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>2023-10-13</t>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Andre Lima Monfrini</t>
+          <t>Echo S Comunicacao Sonora e Visual</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (130 de 143)</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -6849,8 +6850,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F165" s="2" t="n">
-        <v>1200</v>
+      <c r="F165" s="3" t="n">
+        <v>600</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -6859,7 +6860,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(a classificar)\0164_(a classificar)_13-10-2023_R$1.200,00_andre_lima_monfrini.pdf</t>
+          <t>164_a-classificar_08-11-2024_R$600,00_echo-s-comunicacao-sonora-e-visual.pdf</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -6868,19 +6869,19 @@
       <c r="A166" t="n">
         <v>165</v>
       </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>2023-10-13</t>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Felipe G Rosa</t>
+          <t>Roberto F D Avila</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (131 de 143)</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -6888,8 +6889,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F166" s="2" t="n">
-        <v>1200</v>
+      <c r="F166" s="3" t="n">
+        <v>1000</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -6898,7 +6899,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(a classificar)\0165_(a classificar)_13-10-2023_R$1.200,00_felipe_g_rosa.pdf</t>
+          <t>165_a-classificar_08-11-2024_R$1.000,00_roberto-f-d-avila.pdf</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -6907,28 +6908,24 @@
       <c r="A167" t="n">
         <v>166</v>
       </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>2023-10-16</t>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Camila Licariao de Carvalho Braune 4</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>36.584.511/0001-</t>
-        </is>
-      </c>
+          <t>do Contribuinte</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F167" s="2" t="n">
-        <v>3000</v>
+      <c r="F167" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -6937,7 +6934,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(a classificar)\0166_(a classificar)_16-10-2023_R$3.000,00_camila_licariao_de_carvalho_braune_4.pdf</t>
+          <t>166_a-classificar_12-11-2024_R$12,00_do-contribuinte.pdf</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -6946,19 +6943,19 @@
       <c r="A168" t="n">
         <v>167</v>
       </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>2023-10-25</t>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Mog Produtora</t>
+          <t>do Contribuinte</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11400274/0001-94 (5 de 6)</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -6966,8 +6963,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F168" s="2" t="n">
-        <v>10000</v>
+      <c r="F168" s="3" t="n">
+        <v>200</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -6976,7 +6973,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(a classificar)\0167_(a classificar)_25-10-2023_R$10.000,00_mog_produtora.pdf</t>
+          <t>167_a-classificar_14-11-2024_R$200,00_do-contribuinte.pdf</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -6985,19 +6982,19 @@
       <c r="A169" t="n">
         <v>168</v>
       </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>2023-10-31</t>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Luis F Monte Cipullo</t>
+          <t>Marach Servicos Audiovisuais Eireli</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (132 de 143)</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -7005,8 +7002,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F169" s="2" t="n">
-        <v>1020</v>
+      <c r="F169" s="3" t="n">
+        <v>230</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -7015,7 +7012,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(a classificar)\0168_(a classificar)_31-10-2023_R$1.020,00_luis_f_monte_cipullo.pdf</t>
+          <t>168_a-classificar_28-11-2024_R$230,00_marach-servicos-audiovisuais-eireli.pdf</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -7024,19 +7021,19 @@
       <c r="A170" t="n">
         <v>169</v>
       </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>2023-10-31</t>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Andre Lima Monfrini</t>
+          <t>:</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>02.903.707/0001-33</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -7044,8 +7041,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F170" s="2" t="n">
-        <v>1020</v>
+      <c r="F170" s="3" t="n">
+        <v>6400</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -7054,7 +7051,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(a classificar)\0169_(a classificar)_31-10-2023_R$1.020,00_andre_lima_monfrini.pdf</t>
+          <t>169_a-classificar_05-12-2024_R$6.400,00_sem-nome.pdf</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -7063,19 +7060,19 @@
       <c r="A171" t="n">
         <v>170</v>
       </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>2023-10-31</t>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Felipe G Rosa</t>
+          <t>Geisa Silva Jesus</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (133 de 143)</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -7083,8 +7080,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F171" s="2" t="n">
-        <v>1020</v>
+      <c r="F171" s="3" t="n">
+        <v>1500</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -7093,7 +7090,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(a classificar)\0170_(a classificar)_31-10-2023_R$1.020,00_felipe_g_rosa.pdf</t>
+          <t>170_a-classificar_05-12-2024_R$1.500,00_geisa-silva-jesus.pdf</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -7102,19 +7099,19 @@
       <c r="A172" t="n">
         <v>171</v>
       </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>2023-11-08</t>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Bernardo T S Costa</t>
+          <t>:</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>33.641.663/0001-44 (2 de 2)</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -7122,8 +7119,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F172" s="2" t="n">
-        <v>300</v>
+      <c r="F172" s="3" t="n">
+        <v>100</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -7132,7 +7129,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(a classificar)\0171_(a classificar)_08-11-2023_R$300,00_bernardo_t_s_costa.pdf</t>
+          <t>171_a-classificar_10-12-2024_R$100,00_sem-nome.pdf</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -7141,19 +7138,19 @@
       <c r="A173" t="n">
         <v>172</v>
       </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>2023-11-14</t>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Monica G P Moraes</t>
+          <t>Editora e Importadora Musical Fermat</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (134 de 143)</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -7161,8 +7158,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F173" s="2" t="n">
-        <v>3724.74</v>
+      <c r="F173" s="3" t="n">
+        <v>3000</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -7171,7 +7168,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(a classificar)\0172_(a classificar)_14-11-2023_R$3.724,74_monica_g_p_moraes.pdf</t>
+          <t>172_a-classificar_17-12-2024_R$3.000,00_editora-e-importadora-musical-fermat.pdf</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -7180,19 +7177,19 @@
       <c r="A174" t="n">
         <v>173</v>
       </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>2025-02-03</t>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Banco Rendimento S/a</t>
+          <t>Som Livre</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (135 de 143)</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -7200,8 +7197,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F174" s="2" t="n">
-        <v>975.04</v>
+      <c r="F174" s="3" t="n">
+        <v>2000</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -7210,7 +7207,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(a classificar)\0173_(a classificar)_03-02-2025_R$975,04_banco_rendimento_s_a.pdf</t>
+          <t>173_a-classificar_17-12-2024_R$2.000,00_som-livre.pdf</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -7219,19 +7216,19 @@
       <c r="A175" t="n">
         <v>174</v>
       </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>2023-10-30</t>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Brilho</t>
+          <t>Carlos Lyra Edicoes Musicais</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (136 de 143)</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -7239,142 +7236,146 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F175" s="2" t="n">
-        <v>211.5</v>
+      <c r="F175" s="3" t="n">
+        <v>3500</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>DIVERGENTE</t>
+          <t>CONCILIADO</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>PENDENTES\111 - 30-10-2023 - Brilho - Equipamento Luz (diária extra).pdf</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>data bate (2023-10-30) mas valor diverge: extrato R$211.50 vs comprovante R$0.00</t>
-        </is>
-      </c>
+          <t>174_a-classificar_17-12-2024_R$3.500,00_carlos-lyra-edicoes-musicais.pdf</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
         <v>175</v>
       </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>2023-10-05</t>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>EDSON DE CAMARGO (truncado)</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
+          <t>Cotacao D.t.v.m. S/a - Sefic</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>11.400.274/0001-94 (137 de 143)</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F176" s="2" t="n">
-        <v>700</v>
+      <c r="F176" s="3" t="n">
+        <v>8393.299999999999</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>SEM-COMPROVANTE</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr"/>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>comprovante do mesmo valor na data já vinculado a outro débito</t>
-        </is>
-      </c>
+          <t>CONCILIADO</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>175_a-classificar_17-12-2024_R$8.393,30_cotacao-d-t-v-m-s-a-sefic.pdf</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
         <v>176</v>
       </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>2023-10-10</t>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Andre Lima Monfrini (truncado)</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
+          <t>Giovana Amano</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>11.400.274/0001-94 (138 de 143)</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F177" s="2" t="n">
-        <v>500</v>
+      <c r="F177" s="3" t="n">
+        <v>5000</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>SEM-COMPROVANTE</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr"/>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>data/valor não bate</t>
-        </is>
-      </c>
+          <t>CONCILIADO</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>176_a-classificar_26-12-2024_R$5.000,00_giovana-amano.pdf</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
         <v>177</v>
       </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>2023-11-08</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>BERNARDO TAVARES ROSA (truncado)</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-16</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>11400274/0001-94 (6 de 6)</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F178" s="2" t="n">
-        <v>300</v>
+      <c r="F178" s="3" t="n">
+        <v>50</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>SEM-COMPROVANTE</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr"/>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>comprovante do mesmo valor na data já vinculado a outro débito</t>
-        </is>
-      </c>
+          <t>CONCILIADO</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>177_a-classificar_16-01-2025_R$50,00_sem-nome.pdf</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
         <v>178</v>
       </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>2023-09-26</t>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>LUIS FELIPE LABAKI (truncado)</t>
+          <t>BANCO RENDIMENTO S/A (truncado)</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -7383,8 +7384,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F179" s="2" t="n">
-        <v>10000</v>
+      <c r="F179" s="3" t="n">
+        <v>975.04</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
@@ -7394,7 +7395,7 @@
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr">
         <is>
-          <t>data/valor não bate</t>
+          <t>débito no extrato sem comprovante correspondente</t>
         </is>
       </c>
     </row>
@@ -7402,14 +7403,14 @@
       <c r="A180" t="n">
         <v>179</v>
       </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>2023-09-26</t>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>ANA BEATRIZ HERMANSON POMA (truncado)</t>
+          <t>BANCO RENDIMENTO S/A (truncado)</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -7418,8 +7419,8 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F180" s="2" t="n">
-        <v>3000</v>
+      <c r="F180" s="3" t="n">
+        <v>975.04</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -7429,7 +7430,7 @@
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr">
         <is>
-          <t>data/valor não bate</t>
+          <t>débito no extrato sem comprovante correspondente</t>
         </is>
       </c>
     </row>
@@ -7437,89 +7438,97 @@
       <c r="A181" t="n">
         <v>180</v>
       </c>
-      <c r="B181" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
         <is>
           <t>2025-02-03</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>CIRCUNSTANC 1961 FSAMPJFN (truncado)</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
+          <t>Banco Rendimento S/a</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>11.400.274/0001-94 (139 de 143)</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F181" s="2" t="n">
+      <c r="F181" s="3" t="n">
         <v>975.04</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>SEM-COMPROVANTE</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr"/>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>comprovante do mesmo valor na data já vinculado a outro débito</t>
-        </is>
-      </c>
+          <t>CONCILIADO</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>180_a-classificar_03-02-2025_R$975,04_banco-rendimento-s-a.pdf</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
         <v>181</v>
       </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>2025-02-03</t>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>BANCO RENDIMENTO S/A (truncado)</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
+          <t>Ganzah</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>11.400.274/0001-94 (140 de 143)</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F182" s="2" t="n">
-        <v>975.04</v>
+      <c r="F182" s="3" t="n">
+        <v>7000</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>SEM-COMPROVANTE</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr"/>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>comprovante do mesmo valor na data já vinculado a outro débito</t>
-        </is>
-      </c>
+          <t>CONCILIADO</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>181_a-classificar_27-02-2025_R$7.000,00_ganzah.pdf</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
         <v>182</v>
       </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>2023-10-09</t>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Amir Labaki</t>
+          <t>:</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>04.884.574/0001-20</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -7527,42 +7536,38 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F183" s="2" t="n">
-        <v>945.49</v>
+      <c r="F183" s="3" t="n">
+        <v>626.3</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>SEM-EXTRATO</t>
+          <t>CONCILIADO</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(a classificar)\0182_(a classificar)_09-10-2023_R$945,49_amir_labaki.pdf</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>sem débito correspondente</t>
-        </is>
-      </c>
+          <t>182_a-classificar_25-03-2025_R$626,30_sem-nome.pdf</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
         <v>183</v>
       </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>2023-10-16</t>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Camila Licariao de Carvalho Braune 4</t>
+          <t>Giovana Amano</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>36.584.511/0001-</t>
+          <t>11.400.274/0001-94 (141 de 143)</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -7570,42 +7575,38 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F184" s="2" t="n">
+      <c r="F184" s="3" t="n">
         <v>3000</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>SEM-EXTRATO</t>
+          <t>CONCILIADO</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(a classificar)\0183_(a classificar)_16-10-2023_R$3.000,00_camila_licariao_de_carvalho_braune_4.pdf</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>sem débito correspondente</t>
-        </is>
-      </c>
+          <t>183_a-classificar_30-04-2025_R$3.000,00_giovana-amano.pdf</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
         <v>184</v>
       </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>2023-10-25</t>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Mog Produtora</t>
+          <t>Planifilmes Ltda</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (142 de 143)</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -7613,42 +7614,38 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F185" s="2" t="n">
-        <v>10000</v>
+      <c r="F185" s="3" t="n">
+        <v>1200</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>SEM-EXTRATO</t>
+          <t>CONCILIADO</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(a classificar)\0184_(a classificar)_25-10-2023_R$10.000,00_mog_produtora.pdf</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>sem débito correspondente</t>
-        </is>
-      </c>
+          <t>184_a-classificar_30-04-2025_R$1.200,00_planifilmes-ltda.pdf</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
         <v>185</v>
       </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>2023-11-14</t>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Monica G P Moraes</t>
+          <t>Fogo Filmes</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>11.400.274/0001-94</t>
+          <t>11.400.274/0001-94 (143 de 143)</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -7656,24 +7653,20 @@
           <t>(a classificar)</t>
         </is>
       </c>
-      <c r="F186" s="2" t="n">
-        <v>3724.74</v>
+      <c r="F186" s="3" t="n">
+        <v>18093.63</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>SEM-EXTRATO</t>
+          <t>CONCILIADO</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(a classificar)\0185_(a classificar)_14-11-2023_R$3.724,74_monica_g_p_moraes.pdf</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>sem débito correspondente</t>
-        </is>
-      </c>
+          <t>185_a-classificar_07-05-2025_R$18.093,63_fogo-filmes.pdf</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I186"/>
